--- a/Aerodyne_ip_tests_summary.xlsx
+++ b/Aerodyne_ip_tests_summary.xlsx
@@ -1481,7 +1481,7 @@
       <c r="H7" t="inlineStr"/>
       <c r="I7" t="inlineStr">
         <is>
-          <t>Compiled</t>
+          <t>Tested</t>
         </is>
       </c>
       <c r="J7" t="inlineStr"/>

--- a/Aerodyne_ip_tests_summary.xlsx
+++ b/Aerodyne_ip_tests_summary.xlsx
@@ -957,7 +957,7 @@
       <c r="Q4" t="inlineStr"/>
       <c r="R4" t="inlineStr">
         <is>
-          <t>Mid</t>
+          <t>High</t>
         </is>
       </c>
       <c r="S4" t="inlineStr"/>
@@ -978,7 +978,7 @@
       <c r="Z4" t="inlineStr"/>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>Mid</t>
         </is>
       </c>
       <c r="AB4" t="inlineStr"/>
@@ -1006,7 +1006,7 @@
       <c r="AL4" t="inlineStr"/>
       <c r="AM4" t="inlineStr">
         <is>
-          <t>Mid</t>
+          <t>High</t>
         </is>
       </c>
       <c r="AN4" t="inlineStr"/>
@@ -1048,7 +1048,7 @@
       <c r="BD4" t="inlineStr"/>
       <c r="BE4" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>Mid</t>
         </is>
       </c>
       <c r="BF4" t="inlineStr"/>
@@ -1062,7 +1062,7 @@
       <c r="BJ4" t="inlineStr"/>
       <c r="BK4" t="inlineStr">
         <is>
-          <t>Low</t>
+          <t>High</t>
         </is>
       </c>
       <c r="BL4" t="inlineStr"/>
@@ -1076,21 +1076,21 @@
       <c r="BP4" t="inlineStr"/>
       <c r="BQ4" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>Low</t>
         </is>
       </c>
       <c r="BR4" t="inlineStr"/>
       <c r="BS4" t="inlineStr"/>
       <c r="BT4" t="inlineStr">
         <is>
-          <t>Mid</t>
+          <t>High</t>
         </is>
       </c>
       <c r="BU4" t="inlineStr"/>
       <c r="BV4" t="inlineStr"/>
       <c r="BW4" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>Mid</t>
         </is>
       </c>
       <c r="BX4" t="inlineStr"/>
@@ -1323,140 +1323,140 @@
       <c r="Q6" t="inlineStr"/>
       <c r="R6" t="inlineStr">
         <is>
-          <t>PLL_Freerun_Trim</t>
+          <t>Self_regLDO_0v6_Trim</t>
         </is>
       </c>
       <c r="S6" t="inlineStr"/>
       <c r="T6" t="inlineStr"/>
       <c r="U6" t="inlineStr">
         <is>
-          <t>GPADC_Settle_Time_Trim</t>
+          <t>PLL_Freerun_Trim</t>
         </is>
       </c>
       <c r="V6" t="inlineStr"/>
       <c r="W6" t="inlineStr"/>
       <c r="X6" t="inlineStr">
         <is>
-          <t>GPADC_Temp_Off_Trimm</t>
+          <t>FLL_Freerun_Trim</t>
         </is>
       </c>
       <c r="Y6" t="inlineStr"/>
       <c r="Z6" t="inlineStr"/>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>GPADC_Vbat_Gain_Off_Trim</t>
+          <t>GPADC_Settle_Time_Trim</t>
         </is>
       </c>
       <c r="AB6" t="inlineStr"/>
       <c r="AC6" t="inlineStr"/>
       <c r="AD6" t="inlineStr">
         <is>
-          <t>OCP_LS_Trim</t>
+          <t>GPADC_Temp_Off_Trimm</t>
         </is>
       </c>
       <c r="AE6" t="inlineStr"/>
       <c r="AF6" t="inlineStr"/>
       <c r="AG6" t="inlineStr">
         <is>
-          <t>OCP_HS_trim</t>
+          <t>GPADC_Vbat_Gain_Off_Trim</t>
         </is>
       </c>
       <c r="AH6" t="inlineStr"/>
       <c r="AI6" t="inlineStr"/>
       <c r="AJ6" t="inlineStr">
         <is>
-          <t>FLL_Freerun_Trim</t>
+          <t>OCP_LS_Trim</t>
         </is>
       </c>
       <c r="AK6" t="inlineStr"/>
       <c r="AL6" t="inlineStr"/>
       <c r="AM6" t="inlineStr">
         <is>
-          <t>VIS_Storbe_Del_Trim</t>
+          <t>OCP_HS_trim</t>
         </is>
       </c>
       <c r="AN6" t="inlineStr"/>
       <c r="AO6" t="inlineStr"/>
       <c r="AP6" t="inlineStr">
         <is>
-          <t>VIS_OFFSET_VSNS</t>
+          <t>VIS_Storbe_Del_Trim</t>
         </is>
       </c>
       <c r="AQ6" t="inlineStr"/>
       <c r="AR6" t="inlineStr"/>
       <c r="AS6" t="inlineStr">
         <is>
-          <t>VIS_GAIN_VSNS</t>
+          <t>VIS_OFFSET_VSNS</t>
         </is>
       </c>
       <c r="AT6" t="inlineStr"/>
       <c r="AU6" t="inlineStr"/>
       <c r="AV6" t="inlineStr">
         <is>
-          <t>VIS_OFFSET_ISNS</t>
+          <t>VIS_GAIN_VSNS</t>
         </is>
       </c>
       <c r="AW6" t="inlineStr"/>
       <c r="AX6" t="inlineStr"/>
       <c r="AY6" t="inlineStr">
         <is>
-          <t>VIS_GAIN_ISNS</t>
+          <t>VIS_OFFSET_ISNS</t>
         </is>
       </c>
       <c r="AZ6" t="inlineStr"/>
       <c r="BA6" t="inlineStr"/>
       <c r="BB6" t="inlineStr">
         <is>
-          <t>VIS_GAIN_V2I</t>
+          <t>VIS_GAIN_ISNS</t>
         </is>
       </c>
       <c r="BC6" t="inlineStr"/>
       <c r="BD6" t="inlineStr"/>
       <c r="BE6" t="inlineStr">
         <is>
-          <t>Offset_cal_cld_3lvl</t>
+          <t>VIS_GAIN_V2I</t>
         </is>
       </c>
       <c r="BF6" t="inlineStr"/>
       <c r="BG6" t="inlineStr"/>
       <c r="BH6" t="inlineStr">
         <is>
-          <t>Offset_cal_cld_half_gain_3lvl</t>
+          <t>Offset_cal_cld_3lvl</t>
         </is>
       </c>
       <c r="BI6" t="inlineStr"/>
       <c r="BJ6" t="inlineStr"/>
       <c r="BK6" t="inlineStr">
         <is>
-          <t>Offset_cal_cld_5lvl_vcm_comp_on</t>
+          <t>Offset_cal_cld_half_gain_3lvl</t>
         </is>
       </c>
       <c r="BL6" t="inlineStr"/>
       <c r="BM6" t="inlineStr"/>
       <c r="BN6" t="inlineStr">
         <is>
-          <t>Offset_cal_cld_5lvl_half_gain_vcm_comp_on</t>
+          <t>Offset_cal_cld_5lvl_vcm_comp_on</t>
         </is>
       </c>
       <c r="BO6" t="inlineStr"/>
       <c r="BP6" t="inlineStr"/>
       <c r="BQ6" t="inlineStr">
         <is>
-          <t>RCTUNE_48K</t>
+          <t>Offset_cal_cld_5lvl_half_gain_vcm_comp_on</t>
         </is>
       </c>
       <c r="BR6" t="inlineStr"/>
       <c r="BS6" t="inlineStr"/>
       <c r="BT6" t="inlineStr">
         <is>
-          <t>RCTUNE_44P1</t>
+          <t>RCTUNE_48K</t>
         </is>
       </c>
       <c r="BU6" t="inlineStr"/>
       <c r="BV6" t="inlineStr"/>
       <c r="BW6" t="inlineStr">
         <is>
-          <t>Self_regLDO_0v6_Trim</t>
+          <t>RCTUNE_44P1</t>
         </is>
       </c>
       <c r="BX6" t="inlineStr"/>
@@ -1476,7 +1476,11 @@
       </c>
       <c r="D7" t="inlineStr"/>
       <c r="E7" t="inlineStr"/>
-      <c r="F7" t="inlineStr"/>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>Tested</t>
+        </is>
+      </c>
       <c r="G7" t="inlineStr"/>
       <c r="H7" t="inlineStr"/>
       <c r="I7" t="inlineStr">
@@ -1488,31 +1492,35 @@
       <c r="K7" t="inlineStr"/>
       <c r="L7" t="inlineStr">
         <is>
-          <t>Compiled</t>
+          <t>Tested</t>
         </is>
       </c>
       <c r="M7" t="inlineStr"/>
       <c r="N7" t="inlineStr"/>
       <c r="O7" t="inlineStr">
         <is>
-          <t>Compiled</t>
+          <t>Tested</t>
         </is>
       </c>
       <c r="P7" t="inlineStr"/>
       <c r="Q7" t="inlineStr"/>
-      <c r="R7" t="inlineStr"/>
+      <c r="R7" t="inlineStr">
+        <is>
+          <t>Tested</t>
+        </is>
+      </c>
       <c r="S7" t="inlineStr"/>
       <c r="T7" t="inlineStr"/>
       <c r="U7" t="inlineStr">
         <is>
-          <t>Compiled</t>
+          <t>Tested</t>
         </is>
       </c>
       <c r="V7" t="inlineStr"/>
       <c r="W7" t="inlineStr"/>
       <c r="X7" t="inlineStr">
         <is>
-          <t>Verified</t>
+          <t>Tested</t>
         </is>
       </c>
       <c r="Y7" t="inlineStr"/>
@@ -1526,7 +1534,7 @@
       <c r="AC7" t="inlineStr"/>
       <c r="AD7" t="inlineStr">
         <is>
-          <t>Compiled</t>
+          <t>Verified</t>
         </is>
       </c>
       <c r="AE7" t="inlineStr"/>
@@ -1538,7 +1546,11 @@
       </c>
       <c r="AH7" t="inlineStr"/>
       <c r="AI7" t="inlineStr"/>
-      <c r="AJ7" t="inlineStr"/>
+      <c r="AJ7" t="inlineStr">
+        <is>
+          <t>Compiled</t>
+        </is>
+      </c>
       <c r="AK7" t="inlineStr"/>
       <c r="AL7" t="inlineStr"/>
       <c r="AM7" t="inlineStr">
@@ -1569,17 +1581,21 @@
       </c>
       <c r="AW7" t="inlineStr"/>
       <c r="AX7" t="inlineStr"/>
-      <c r="AY7" t="inlineStr"/>
+      <c r="AY7" t="inlineStr">
+        <is>
+          <t>Compiled</t>
+        </is>
+      </c>
       <c r="AZ7" t="inlineStr"/>
       <c r="BA7" t="inlineStr"/>
-      <c r="BB7" t="inlineStr">
-        <is>
-          <t>Compiled</t>
-        </is>
-      </c>
+      <c r="BB7" t="inlineStr"/>
       <c r="BC7" t="inlineStr"/>
       <c r="BD7" t="inlineStr"/>
-      <c r="BE7" t="inlineStr"/>
+      <c r="BE7" t="inlineStr">
+        <is>
+          <t>Compiled</t>
+        </is>
+      </c>
       <c r="BF7" t="inlineStr"/>
       <c r="BG7" t="inlineStr"/>
       <c r="BH7" t="inlineStr"/>
@@ -1597,11 +1613,7 @@
       <c r="BT7" t="inlineStr"/>
       <c r="BU7" t="inlineStr"/>
       <c r="BV7" t="inlineStr"/>
-      <c r="BW7" t="inlineStr">
-        <is>
-          <t>Compiled</t>
-        </is>
-      </c>
+      <c r="BW7" t="inlineStr"/>
       <c r="BX7" t="inlineStr"/>
       <c r="BY7" t="inlineStr"/>
     </row>
@@ -1656,56 +1668,56 @@
       <c r="T8" t="inlineStr"/>
       <c r="U8" t="inlineStr">
         <is>
-          <t>IOCLK1</t>
+          <t>IODATA1</t>
         </is>
       </c>
       <c r="V8" t="inlineStr"/>
       <c r="W8" t="inlineStr"/>
       <c r="X8" t="inlineStr">
         <is>
-          <t>Register read</t>
+          <t>ADDR</t>
         </is>
       </c>
       <c r="Y8" t="inlineStr"/>
       <c r="Z8" t="inlineStr"/>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>Register read</t>
+          <t>IOCLK1</t>
         </is>
       </c>
       <c r="AB8" t="inlineStr"/>
       <c r="AC8" t="inlineStr"/>
       <c r="AD8" t="inlineStr">
         <is>
-          <t>IODATA1</t>
+          <t>Register read</t>
         </is>
       </c>
       <c r="AE8" t="inlineStr"/>
       <c r="AF8" t="inlineStr"/>
       <c r="AG8" t="inlineStr">
         <is>
-          <t>IODATA1</t>
+          <t>Register read</t>
         </is>
       </c>
       <c r="AH8" t="inlineStr"/>
       <c r="AI8" t="inlineStr"/>
       <c r="AJ8" t="inlineStr">
         <is>
-          <t>ADDR</t>
+          <t>IODATA1</t>
         </is>
       </c>
       <c r="AK8" t="inlineStr"/>
       <c r="AL8" t="inlineStr"/>
       <c r="AM8" t="inlineStr">
         <is>
-          <t>IOCLK1</t>
+          <t>IODATA1</t>
         </is>
       </c>
       <c r="AN8" t="inlineStr"/>
       <c r="AO8" t="inlineStr"/>
       <c r="AP8" t="inlineStr">
         <is>
-          <t>Register read</t>
+          <t>IOCLK1</t>
         </is>
       </c>
       <c r="AQ8" t="inlineStr"/>
@@ -1740,7 +1752,7 @@
       <c r="BD8" t="inlineStr"/>
       <c r="BE8" t="inlineStr">
         <is>
-          <t>Automatic routine</t>
+          <t>Register read</t>
         </is>
       </c>
       <c r="BF8" t="inlineStr"/>
@@ -1780,7 +1792,11 @@
       </c>
       <c r="BU8" t="inlineStr"/>
       <c r="BV8" t="inlineStr"/>
-      <c r="BW8" t="inlineStr"/>
+      <c r="BW8" t="inlineStr">
+        <is>
+          <t>Automatic routine</t>
+        </is>
+      </c>
       <c r="BX8" t="inlineStr"/>
       <c r="BY8" t="inlineStr"/>
     </row>
@@ -1826,11 +1842,7 @@
       </c>
       <c r="P9" t="inlineStr"/>
       <c r="Q9" t="inlineStr"/>
-      <c r="R9" t="inlineStr">
-        <is>
-          <t>Clock</t>
-        </is>
-      </c>
+      <c r="R9" t="inlineStr"/>
       <c r="S9" t="inlineStr"/>
       <c r="T9" t="inlineStr"/>
       <c r="U9" t="inlineStr">
@@ -1842,14 +1854,14 @@
       <c r="W9" t="inlineStr"/>
       <c r="X9" t="inlineStr">
         <is>
-          <t>DC</t>
+          <t>Clock</t>
         </is>
       </c>
       <c r="Y9" t="inlineStr"/>
       <c r="Z9" t="inlineStr"/>
       <c r="AA9" t="inlineStr">
         <is>
-          <t>DC</t>
+          <t>Clock</t>
         </is>
       </c>
       <c r="AB9" t="inlineStr"/>
@@ -1870,21 +1882,21 @@
       <c r="AI9" t="inlineStr"/>
       <c r="AJ9" t="inlineStr">
         <is>
-          <t>Clock</t>
+          <t>DC</t>
         </is>
       </c>
       <c r="AK9" t="inlineStr"/>
       <c r="AL9" t="inlineStr"/>
       <c r="AM9" t="inlineStr">
         <is>
-          <t>Clock</t>
+          <t>DC</t>
         </is>
       </c>
       <c r="AN9" t="inlineStr"/>
       <c r="AO9" t="inlineStr"/>
       <c r="AP9" t="inlineStr">
         <is>
-          <t>DC</t>
+          <t>Clock</t>
         </is>
       </c>
       <c r="AQ9" t="inlineStr"/>
@@ -1945,7 +1957,11 @@
       </c>
       <c r="BO9" t="inlineStr"/>
       <c r="BP9" t="inlineStr"/>
-      <c r="BQ9" t="inlineStr"/>
+      <c r="BQ9" t="inlineStr">
+        <is>
+          <t>DC</t>
+        </is>
+      </c>
       <c r="BR9" t="inlineStr"/>
       <c r="BS9" t="inlineStr"/>
       <c r="BT9" t="inlineStr"/>
@@ -1989,7 +2005,11 @@
       </c>
       <c r="P10" t="inlineStr"/>
       <c r="Q10" t="inlineStr"/>
-      <c r="R10" t="inlineStr"/>
+      <c r="R10" t="inlineStr">
+        <is>
+          <t>0.596</t>
+        </is>
+      </c>
       <c r="S10" t="inlineStr"/>
       <c r="T10" t="inlineStr"/>
       <c r="U10" t="inlineStr"/>
@@ -2001,24 +2021,24 @@
       <c r="AA10" t="inlineStr"/>
       <c r="AB10" t="inlineStr"/>
       <c r="AC10" t="inlineStr"/>
-      <c r="AD10" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
+      <c r="AD10" t="inlineStr"/>
       <c r="AE10" t="inlineStr"/>
       <c r="AF10" t="inlineStr"/>
-      <c r="AG10" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
+      <c r="AG10" t="inlineStr"/>
       <c r="AH10" t="inlineStr"/>
       <c r="AI10" t="inlineStr"/>
-      <c r="AJ10" t="inlineStr"/>
+      <c r="AJ10" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
       <c r="AK10" t="inlineStr"/>
       <c r="AL10" t="inlineStr"/>
-      <c r="AM10" t="inlineStr"/>
+      <c r="AM10" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
       <c r="AN10" t="inlineStr"/>
       <c r="AO10" t="inlineStr"/>
       <c r="AP10" t="inlineStr"/>
@@ -2036,11 +2056,7 @@
       <c r="BB10" t="inlineStr"/>
       <c r="BC10" t="inlineStr"/>
       <c r="BD10" t="inlineStr"/>
-      <c r="BE10" t="inlineStr">
-        <is>
-          <t>-2</t>
-        </is>
-      </c>
+      <c r="BE10" t="inlineStr"/>
       <c r="BF10" t="inlineStr"/>
       <c r="BG10" t="inlineStr"/>
       <c r="BH10" t="inlineStr">
@@ -2064,17 +2080,17 @@
       </c>
       <c r="BO10" t="inlineStr"/>
       <c r="BP10" t="inlineStr"/>
-      <c r="BQ10" t="inlineStr"/>
+      <c r="BQ10" t="inlineStr">
+        <is>
+          <t>-2</t>
+        </is>
+      </c>
       <c r="BR10" t="inlineStr"/>
       <c r="BS10" t="inlineStr"/>
       <c r="BT10" t="inlineStr"/>
       <c r="BU10" t="inlineStr"/>
       <c r="BV10" t="inlineStr"/>
-      <c r="BW10" t="inlineStr">
-        <is>
-          <t>0.596</t>
-        </is>
-      </c>
+      <c r="BW10" t="inlineStr"/>
       <c r="BX10" t="inlineStr"/>
       <c r="BY10" t="inlineStr"/>
     </row>
@@ -2122,53 +2138,57 @@
       <c r="Q11" t="inlineStr"/>
       <c r="R11" t="inlineStr">
         <is>
-          <t>12.288</t>
+          <t>0.6</t>
         </is>
       </c>
       <c r="S11" t="inlineStr"/>
       <c r="T11" t="inlineStr"/>
       <c r="U11" t="inlineStr">
         <is>
-          <t>9.09</t>
+          <t>12.288</t>
         </is>
       </c>
       <c r="V11" t="inlineStr"/>
       <c r="W11" t="inlineStr"/>
-      <c r="X11" t="inlineStr"/>
+      <c r="X11" t="inlineStr">
+        <is>
+          <t>289.27</t>
+        </is>
+      </c>
       <c r="Y11" t="inlineStr"/>
       <c r="Z11" t="inlineStr"/>
-      <c r="AA11" t="inlineStr"/>
+      <c r="AA11" t="inlineStr">
+        <is>
+          <t>9.09</t>
+        </is>
+      </c>
       <c r="AB11" t="inlineStr"/>
       <c r="AC11" t="inlineStr"/>
-      <c r="AD11" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
+      <c r="AD11" t="inlineStr"/>
       <c r="AE11" t="inlineStr"/>
       <c r="AF11" t="inlineStr"/>
-      <c r="AG11" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
+      <c r="AG11" t="inlineStr"/>
       <c r="AH11" t="inlineStr"/>
       <c r="AI11" t="inlineStr"/>
       <c r="AJ11" t="inlineStr">
         <is>
-          <t>289.27</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AK11" t="inlineStr"/>
       <c r="AL11" t="inlineStr"/>
       <c r="AM11" t="inlineStr">
         <is>
-          <t>3.846</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AN11" t="inlineStr"/>
       <c r="AO11" t="inlineStr"/>
-      <c r="AP11" t="inlineStr"/>
+      <c r="AP11" t="inlineStr">
+        <is>
+          <t>3.846</t>
+        </is>
+      </c>
       <c r="AQ11" t="inlineStr"/>
       <c r="AR11" t="inlineStr"/>
       <c r="AS11" t="inlineStr"/>
@@ -2195,11 +2215,7 @@
       <c r="BN11" t="inlineStr"/>
       <c r="BO11" t="inlineStr"/>
       <c r="BP11" t="inlineStr"/>
-      <c r="BQ11" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
+      <c r="BQ11" t="inlineStr"/>
       <c r="BR11" t="inlineStr"/>
       <c r="BS11" t="inlineStr"/>
       <c r="BT11" t="inlineStr">
@@ -2211,7 +2227,7 @@
       <c r="BV11" t="inlineStr"/>
       <c r="BW11" t="inlineStr">
         <is>
-          <t>0.6</t>
+          <t>8</t>
         </is>
       </c>
       <c r="BX11" t="inlineStr"/>
@@ -2251,7 +2267,11 @@
       </c>
       <c r="P12" t="inlineStr"/>
       <c r="Q12" t="inlineStr"/>
-      <c r="R12" t="inlineStr"/>
+      <c r="R12" t="inlineStr">
+        <is>
+          <t>0.604</t>
+        </is>
+      </c>
       <c r="S12" t="inlineStr"/>
       <c r="T12" t="inlineStr"/>
       <c r="U12" t="inlineStr"/>
@@ -2263,24 +2283,24 @@
       <c r="AA12" t="inlineStr"/>
       <c r="AB12" t="inlineStr"/>
       <c r="AC12" t="inlineStr"/>
-      <c r="AD12" t="inlineStr">
-        <is>
-          <t>15</t>
-        </is>
-      </c>
+      <c r="AD12" t="inlineStr"/>
       <c r="AE12" t="inlineStr"/>
       <c r="AF12" t="inlineStr"/>
-      <c r="AG12" t="inlineStr">
-        <is>
-          <t>15</t>
-        </is>
-      </c>
+      <c r="AG12" t="inlineStr"/>
       <c r="AH12" t="inlineStr"/>
       <c r="AI12" t="inlineStr"/>
-      <c r="AJ12" t="inlineStr"/>
+      <c r="AJ12" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
       <c r="AK12" t="inlineStr"/>
       <c r="AL12" t="inlineStr"/>
-      <c r="AM12" t="inlineStr"/>
+      <c r="AM12" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
       <c r="AN12" t="inlineStr"/>
       <c r="AO12" t="inlineStr"/>
       <c r="AP12" t="inlineStr"/>
@@ -2298,11 +2318,7 @@
       <c r="BB12" t="inlineStr"/>
       <c r="BC12" t="inlineStr"/>
       <c r="BD12" t="inlineStr"/>
-      <c r="BE12" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
+      <c r="BE12" t="inlineStr"/>
       <c r="BF12" t="inlineStr"/>
       <c r="BG12" t="inlineStr"/>
       <c r="BH12" t="inlineStr">
@@ -2326,17 +2342,17 @@
       </c>
       <c r="BO12" t="inlineStr"/>
       <c r="BP12" t="inlineStr"/>
-      <c r="BQ12" t="inlineStr"/>
+      <c r="BQ12" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="BR12" t="inlineStr"/>
       <c r="BS12" t="inlineStr"/>
       <c r="BT12" t="inlineStr"/>
       <c r="BU12" t="inlineStr"/>
       <c r="BV12" t="inlineStr"/>
-      <c r="BW12" t="inlineStr">
-        <is>
-          <t>0.604</t>
-        </is>
-      </c>
+      <c r="BW12" t="inlineStr"/>
       <c r="BX12" t="inlineStr"/>
       <c r="BY12" t="inlineStr"/>
     </row>
@@ -2384,7 +2400,7 @@
       <c r="Q13" t="inlineStr"/>
       <c r="R13" t="inlineStr">
         <is>
-          <t>MHz</t>
+          <t>V</t>
         </is>
       </c>
       <c r="S13" t="inlineStr"/>
@@ -2398,12 +2414,16 @@
       <c r="W13" t="inlineStr"/>
       <c r="X13" t="inlineStr">
         <is>
-          <t>bits</t>
+          <t>kHz</t>
         </is>
       </c>
       <c r="Y13" t="inlineStr"/>
       <c r="Z13" t="inlineStr"/>
-      <c r="AA13" t="inlineStr"/>
+      <c r="AA13" t="inlineStr">
+        <is>
+          <t>MHz</t>
+        </is>
+      </c>
       <c r="AB13" t="inlineStr"/>
       <c r="AC13" t="inlineStr"/>
       <c r="AD13" t="inlineStr">
@@ -2413,28 +2433,28 @@
       </c>
       <c r="AE13" t="inlineStr"/>
       <c r="AF13" t="inlineStr"/>
-      <c r="AG13" t="inlineStr">
-        <is>
-          <t>bits</t>
-        </is>
-      </c>
+      <c r="AG13" t="inlineStr"/>
       <c r="AH13" t="inlineStr"/>
       <c r="AI13" t="inlineStr"/>
       <c r="AJ13" t="inlineStr">
         <is>
-          <t>kHz</t>
+          <t>bits</t>
         </is>
       </c>
       <c r="AK13" t="inlineStr"/>
       <c r="AL13" t="inlineStr"/>
       <c r="AM13" t="inlineStr">
         <is>
-          <t>MHz</t>
+          <t>bits</t>
         </is>
       </c>
       <c r="AN13" t="inlineStr"/>
       <c r="AO13" t="inlineStr"/>
-      <c r="AP13" t="inlineStr"/>
+      <c r="AP13" t="inlineStr">
+        <is>
+          <t>MHz</t>
+        </is>
+      </c>
       <c r="AQ13" t="inlineStr"/>
       <c r="AR13" t="inlineStr"/>
       <c r="AS13" t="inlineStr"/>
@@ -2449,11 +2469,7 @@
       <c r="BB13" t="inlineStr"/>
       <c r="BC13" t="inlineStr"/>
       <c r="BD13" t="inlineStr"/>
-      <c r="BE13" t="inlineStr">
-        <is>
-          <t>mV</t>
-        </is>
-      </c>
+      <c r="BE13" t="inlineStr"/>
       <c r="BF13" t="inlineStr"/>
       <c r="BG13" t="inlineStr"/>
       <c r="BH13" t="inlineStr">
@@ -2479,7 +2495,7 @@
       <c r="BP13" t="inlineStr"/>
       <c r="BQ13" t="inlineStr">
         <is>
-          <t>bits</t>
+          <t>mV</t>
         </is>
       </c>
       <c r="BR13" t="inlineStr"/>
@@ -2493,7 +2509,7 @@
       <c r="BV13" t="inlineStr"/>
       <c r="BW13" t="inlineStr">
         <is>
-          <t>V</t>
+          <t>bits</t>
         </is>
       </c>
       <c r="BX13" t="inlineStr"/>
@@ -2537,11 +2553,7 @@
       </c>
       <c r="P14" t="inlineStr"/>
       <c r="Q14" t="inlineStr"/>
-      <c r="R14" t="inlineStr">
-        <is>
-          <t>10kHz resolution</t>
-        </is>
-      </c>
+      <c r="R14" t="inlineStr"/>
       <c r="S14" t="inlineStr"/>
       <c r="T14" t="inlineStr"/>
       <c r="U14" t="inlineStr">
@@ -2551,10 +2563,18 @@
       </c>
       <c r="V14" t="inlineStr"/>
       <c r="W14" t="inlineStr"/>
-      <c r="X14" t="inlineStr"/>
+      <c r="X14" t="inlineStr">
+        <is>
+          <t>0.5kHz resolution</t>
+        </is>
+      </c>
       <c r="Y14" t="inlineStr"/>
       <c r="Z14" t="inlineStr"/>
-      <c r="AA14" t="inlineStr"/>
+      <c r="AA14" t="inlineStr">
+        <is>
+          <t>10kHz resolution</t>
+        </is>
+      </c>
       <c r="AB14" t="inlineStr"/>
       <c r="AC14" t="inlineStr"/>
       <c r="AD14" t="inlineStr"/>
@@ -2563,21 +2583,17 @@
       <c r="AG14" t="inlineStr"/>
       <c r="AH14" t="inlineStr"/>
       <c r="AI14" t="inlineStr"/>
-      <c r="AJ14" t="inlineStr">
-        <is>
-          <t>0.5kHz resolution</t>
-        </is>
-      </c>
+      <c r="AJ14" t="inlineStr"/>
       <c r="AK14" t="inlineStr"/>
       <c r="AL14" t="inlineStr"/>
-      <c r="AM14" t="inlineStr">
-        <is>
-          <t>10kHz resolution</t>
-        </is>
-      </c>
+      <c r="AM14" t="inlineStr"/>
       <c r="AN14" t="inlineStr"/>
       <c r="AO14" t="inlineStr"/>
-      <c r="AP14" t="inlineStr"/>
+      <c r="AP14" t="inlineStr">
+        <is>
+          <t>10kHz resolution</t>
+        </is>
+      </c>
       <c r="AQ14" t="inlineStr"/>
       <c r="AR14" t="inlineStr"/>
       <c r="AS14" t="inlineStr"/>
@@ -3337,56 +3353,64 @@
       <c r="Q21" t="inlineStr"/>
       <c r="R21" t="inlineStr">
         <is>
+          <t>Measure Voltage</t>
+        </is>
+      </c>
+      <c r="S21" t="inlineStr">
+        <is>
+          <t>V</t>
+        </is>
+      </c>
+      <c r="T21" t="inlineStr"/>
+      <c r="U21" t="inlineStr">
+        <is>
           <t>Measure Frequency</t>
         </is>
       </c>
-      <c r="S21" t="inlineStr">
+      <c r="V21" t="inlineStr">
         <is>
           <t>MHz</t>
         </is>
       </c>
-      <c r="T21" t="inlineStr">
+      <c r="W21" t="inlineStr">
         <is>
           <t>Measure 12.288MHz Output Clock</t>
         </is>
       </c>
-      <c r="U21" t="inlineStr"/>
-      <c r="V21" t="inlineStr"/>
-      <c r="W21" t="inlineStr"/>
       <c r="X21" t="inlineStr"/>
       <c r="Y21" t="inlineStr"/>
       <c r="Z21" t="inlineStr"/>
       <c r="AA21" t="inlineStr"/>
       <c r="AB21" t="inlineStr"/>
       <c r="AC21" t="inlineStr"/>
-      <c r="AD21" t="inlineStr">
+      <c r="AD21" t="inlineStr"/>
+      <c r="AE21" t="inlineStr"/>
+      <c r="AF21" t="inlineStr"/>
+      <c r="AG21" t="inlineStr"/>
+      <c r="AH21" t="inlineStr"/>
+      <c r="AI21" t="inlineStr"/>
+      <c r="AJ21" t="inlineStr">
         <is>
           <t>VMEASURE</t>
         </is>
       </c>
-      <c r="AE21" t="inlineStr"/>
-      <c r="AF21" t="inlineStr">
+      <c r="AK21" t="inlineStr"/>
+      <c r="AL21" t="inlineStr">
         <is>
           <t>Logical Values</t>
         </is>
       </c>
-      <c r="AG21" t="inlineStr">
+      <c r="AM21" t="inlineStr">
         <is>
           <t>VMEASURE</t>
         </is>
       </c>
-      <c r="AH21" t="inlineStr"/>
-      <c r="AI21" t="inlineStr">
+      <c r="AN21" t="inlineStr"/>
+      <c r="AO21" t="inlineStr">
         <is>
           <t>Logical Value</t>
         </is>
       </c>
-      <c r="AJ21" t="inlineStr"/>
-      <c r="AK21" t="inlineStr"/>
-      <c r="AL21" t="inlineStr"/>
-      <c r="AM21" t="inlineStr"/>
-      <c r="AN21" t="inlineStr"/>
-      <c r="AO21" t="inlineStr"/>
       <c r="AP21" t="inlineStr"/>
       <c r="AQ21" t="inlineStr"/>
       <c r="AR21" t="inlineStr"/>
@@ -3420,16 +3444,8 @@
       <c r="BT21" t="inlineStr"/>
       <c r="BU21" t="inlineStr"/>
       <c r="BV21" t="inlineStr"/>
-      <c r="BW21" t="inlineStr">
-        <is>
-          <t>Measure Voltage</t>
-        </is>
-      </c>
-      <c r="BX21" t="inlineStr">
-        <is>
-          <t>V</t>
-        </is>
-      </c>
+      <c r="BW21" t="inlineStr"/>
+      <c r="BX21" t="inlineStr"/>
       <c r="BY21" t="inlineStr"/>
     </row>
     <row r="22">
@@ -3954,16 +3970,8 @@
       <c r="AM24" t="inlineStr"/>
       <c r="AN24" t="inlineStr"/>
       <c r="AO24" t="inlineStr"/>
-      <c r="AP24" t="inlineStr">
-        <is>
-          <t>1.85</t>
-        </is>
-      </c>
-      <c r="AQ24" t="inlineStr">
-        <is>
-          <t>V</t>
-        </is>
-      </c>
+      <c r="AP24" t="inlineStr"/>
+      <c r="AQ24" t="inlineStr"/>
       <c r="AR24" t="inlineStr"/>
       <c r="AS24" t="inlineStr">
         <is>
@@ -4009,8 +4017,16 @@
         </is>
       </c>
       <c r="BD24" t="inlineStr"/>
-      <c r="BE24" t="inlineStr"/>
-      <c r="BF24" t="inlineStr"/>
+      <c r="BE24" t="inlineStr">
+        <is>
+          <t>1.85</t>
+        </is>
+      </c>
+      <c r="BF24" t="inlineStr">
+        <is>
+          <t>V</t>
+        </is>
+      </c>
       <c r="BG24" t="inlineStr"/>
       <c r="BH24" t="inlineStr"/>
       <c r="BI24" t="inlineStr"/>
@@ -4056,33 +4072,17 @@
       <c r="P25" t="inlineStr"/>
       <c r="Q25" t="inlineStr"/>
       <c r="R25" t="inlineStr"/>
-      <c r="S25" t="inlineStr">
+      <c r="S25" t="inlineStr"/>
+      <c r="T25" t="inlineStr"/>
+      <c r="U25" t="inlineStr"/>
+      <c r="V25" t="inlineStr">
         <is>
           <t>MHz</t>
         </is>
       </c>
-      <c r="T25" t="inlineStr"/>
-      <c r="U25" t="inlineStr">
-        <is>
-          <t>12.288</t>
-        </is>
-      </c>
-      <c r="V25" t="inlineStr">
-        <is>
-          <t>MHz</t>
-        </is>
-      </c>
       <c r="W25" t="inlineStr"/>
-      <c r="X25" t="inlineStr">
-        <is>
-          <t>12.288</t>
-        </is>
-      </c>
-      <c r="Y25" t="inlineStr">
-        <is>
-          <t>MHz</t>
-        </is>
-      </c>
+      <c r="X25" t="inlineStr"/>
+      <c r="Y25" t="inlineStr"/>
       <c r="Z25" t="inlineStr"/>
       <c r="AA25" t="inlineStr">
         <is>
@@ -4095,25 +4095,33 @@
         </is>
       </c>
       <c r="AC25" t="inlineStr"/>
-      <c r="AD25" t="inlineStr"/>
-      <c r="AE25" t="inlineStr"/>
+      <c r="AD25" t="inlineStr">
+        <is>
+          <t>12.288</t>
+        </is>
+      </c>
+      <c r="AE25" t="inlineStr">
+        <is>
+          <t>MHz</t>
+        </is>
+      </c>
       <c r="AF25" t="inlineStr"/>
-      <c r="AG25" t="inlineStr"/>
-      <c r="AH25" t="inlineStr"/>
+      <c r="AG25" t="inlineStr">
+        <is>
+          <t>12.288</t>
+        </is>
+      </c>
+      <c r="AH25" t="inlineStr">
+        <is>
+          <t>MHz</t>
+        </is>
+      </c>
       <c r="AI25" t="inlineStr"/>
       <c r="AJ25" t="inlineStr"/>
       <c r="AK25" t="inlineStr"/>
       <c r="AL25" t="inlineStr"/>
-      <c r="AM25" t="inlineStr">
-        <is>
-          <t>3.072</t>
-        </is>
-      </c>
-      <c r="AN25" t="inlineStr">
-        <is>
-          <t>MHz</t>
-        </is>
-      </c>
+      <c r="AM25" t="inlineStr"/>
+      <c r="AN25" t="inlineStr"/>
       <c r="AO25" t="inlineStr"/>
       <c r="AP25" t="inlineStr">
         <is>
@@ -4216,7 +4224,7 @@
       <c r="BP25" t="inlineStr"/>
       <c r="BQ25" t="inlineStr">
         <is>
-          <t>12.288</t>
+          <t>3.072</t>
         </is>
       </c>
       <c r="BR25" t="inlineStr">
@@ -4227,17 +4235,25 @@
       <c r="BS25" t="inlineStr"/>
       <c r="BT25" t="inlineStr">
         <is>
+          <t>12.288</t>
+        </is>
+      </c>
+      <c r="BU25" t="inlineStr">
+        <is>
+          <t>MHz</t>
+        </is>
+      </c>
+      <c r="BV25" t="inlineStr"/>
+      <c r="BW25" t="inlineStr">
+        <is>
           <t>11.2896</t>
         </is>
       </c>
-      <c r="BU25" t="inlineStr">
+      <c r="BX25" t="inlineStr">
         <is>
           <t>MHz</t>
         </is>
       </c>
-      <c r="BV25" t="inlineStr"/>
-      <c r="BW25" t="inlineStr"/>
-      <c r="BX25" t="inlineStr"/>
       <c r="BY25" t="inlineStr"/>
     </row>
     <row r="26">
@@ -4320,7 +4336,11 @@
           <t>V</t>
         </is>
       </c>
-      <c r="T26" t="inlineStr"/>
+      <c r="T26" t="inlineStr">
+        <is>
+          <t>pin current=6.44e-6A</t>
+        </is>
+      </c>
       <c r="U26" t="n">
         <v>3.7</v>
       </c>
@@ -4339,21 +4359,15 @@
         </is>
       </c>
       <c r="Z26" t="inlineStr"/>
-      <c r="AA26" t="inlineStr">
-        <is>
-          <t>2.8</t>
-        </is>
+      <c r="AA26" t="n">
+        <v>3.7</v>
       </c>
       <c r="AB26" t="inlineStr">
         <is>
           <t>V</t>
         </is>
       </c>
-      <c r="AC26" t="inlineStr">
-        <is>
-          <t>Step from 2.8V to 4.8V</t>
-        </is>
-      </c>
+      <c r="AC26" t="inlineStr"/>
       <c r="AD26" t="n">
         <v>3.7</v>
       </c>
@@ -4363,15 +4377,21 @@
         </is>
       </c>
       <c r="AF26" t="inlineStr"/>
-      <c r="AG26" t="n">
-        <v>3.7</v>
+      <c r="AG26" t="inlineStr">
+        <is>
+          <t>2.8</t>
+        </is>
       </c>
       <c r="AH26" t="inlineStr">
         <is>
           <t>V</t>
         </is>
       </c>
-      <c r="AI26" t="inlineStr"/>
+      <c r="AI26" t="inlineStr">
+        <is>
+          <t>Step from 2.8V to 4.8V</t>
+        </is>
+      </c>
       <c r="AJ26" t="n">
         <v>3.7</v>
       </c>
@@ -4497,11 +4517,7 @@
           <t>V</t>
         </is>
       </c>
-      <c r="BY26" t="inlineStr">
-        <is>
-          <t>pin current=6.44e-6A</t>
-        </is>
-      </c>
+      <c r="BY26" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" t="n">
@@ -4590,21 +4606,15 @@
         </is>
       </c>
       <c r="Z27" t="inlineStr"/>
-      <c r="AA27" t="inlineStr">
-        <is>
-          <t>2.8</t>
-        </is>
+      <c r="AA27" t="n">
+        <v>3.7</v>
       </c>
       <c r="AB27" t="inlineStr">
         <is>
           <t>V</t>
         </is>
       </c>
-      <c r="AC27" t="inlineStr">
-        <is>
-          <t>Step from 2.8V to 4.8V</t>
-        </is>
-      </c>
+      <c r="AC27" t="inlineStr"/>
       <c r="AD27" t="n">
         <v>3.7</v>
       </c>
@@ -4614,15 +4624,21 @@
         </is>
       </c>
       <c r="AF27" t="inlineStr"/>
-      <c r="AG27" t="n">
-        <v>3.7</v>
+      <c r="AG27" t="inlineStr">
+        <is>
+          <t>2.8</t>
+        </is>
       </c>
       <c r="AH27" t="inlineStr">
         <is>
           <t>V</t>
         </is>
       </c>
-      <c r="AI27" t="inlineStr"/>
+      <c r="AI27" t="inlineStr">
+        <is>
+          <t>Step from 2.8V to 4.8V</t>
+        </is>
+      </c>
       <c r="AJ27" t="n">
         <v>3.7</v>
       </c>
@@ -4788,7 +4804,11 @@
       <c r="U28" t="inlineStr"/>
       <c r="V28" t="inlineStr"/>
       <c r="W28" t="inlineStr"/>
-      <c r="X28" t="inlineStr"/>
+      <c r="X28" t="inlineStr">
+        <is>
+          <t>Measure frequency</t>
+        </is>
+      </c>
       <c r="Y28" t="inlineStr"/>
       <c r="Z28" t="inlineStr"/>
       <c r="AA28" t="inlineStr"/>
@@ -4800,11 +4820,7 @@
       <c r="AG28" t="inlineStr"/>
       <c r="AH28" t="inlineStr"/>
       <c r="AI28" t="inlineStr"/>
-      <c r="AJ28" t="inlineStr">
-        <is>
-          <t>Measure frequency</t>
-        </is>
-      </c>
+      <c r="AJ28" t="inlineStr"/>
       <c r="AK28" t="inlineStr"/>
       <c r="AL28" t="inlineStr"/>
       <c r="AM28" t="inlineStr"/>
@@ -4933,16 +4949,8 @@
         </is>
       </c>
       <c r="W29" t="inlineStr"/>
-      <c r="X29" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="Y29" t="inlineStr">
-        <is>
-          <t>V</t>
-        </is>
-      </c>
+      <c r="X29" t="inlineStr"/>
+      <c r="Y29" t="inlineStr"/>
       <c r="Z29" t="inlineStr"/>
       <c r="AA29" t="inlineStr">
         <is>
@@ -4977,8 +4985,16 @@
         </is>
       </c>
       <c r="AI29" t="inlineStr"/>
-      <c r="AJ29" t="inlineStr"/>
-      <c r="AK29" t="inlineStr"/>
+      <c r="AJ29" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AK29" t="inlineStr">
+        <is>
+          <t>V</t>
+        </is>
+      </c>
       <c r="AL29" t="inlineStr"/>
       <c r="AM29" t="inlineStr">
         <is>
@@ -5210,16 +5226,8 @@
         </is>
       </c>
       <c r="W30" t="inlineStr"/>
-      <c r="X30" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="Y30" t="inlineStr">
-        <is>
-          <t>V</t>
-        </is>
-      </c>
+      <c r="X30" t="inlineStr"/>
+      <c r="Y30" t="inlineStr"/>
       <c r="Z30" t="inlineStr"/>
       <c r="AA30" t="inlineStr">
         <is>
@@ -5254,8 +5262,16 @@
         </is>
       </c>
       <c r="AI30" t="inlineStr"/>
-      <c r="AJ30" t="inlineStr"/>
-      <c r="AK30" t="inlineStr"/>
+      <c r="AJ30" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AK30" t="inlineStr">
+        <is>
+          <t>V</t>
+        </is>
+      </c>
       <c r="AL30" t="inlineStr"/>
       <c r="AM30" t="inlineStr">
         <is>
@@ -5437,80 +5453,80 @@
       <c r="AA31" t="inlineStr"/>
       <c r="AB31" t="inlineStr"/>
       <c r="AC31" t="inlineStr"/>
-      <c r="AD31" t="inlineStr">
+      <c r="AD31" t="inlineStr"/>
+      <c r="AE31" t="inlineStr"/>
+      <c r="AF31" t="inlineStr"/>
+      <c r="AG31" t="inlineStr"/>
+      <c r="AH31" t="inlineStr"/>
+      <c r="AI31" t="inlineStr"/>
+      <c r="AJ31" t="inlineStr">
         <is>
           <t>500</t>
         </is>
       </c>
-      <c r="AE31" t="inlineStr">
+      <c r="AK31" t="inlineStr">
         <is>
           <t>mA</t>
         </is>
       </c>
-      <c r="AF31" t="inlineStr">
+      <c r="AL31" t="inlineStr">
         <is>
           <t>force current into OUTP</t>
         </is>
       </c>
-      <c r="AG31" t="inlineStr">
+      <c r="AM31" t="inlineStr">
         <is>
           <t>500</t>
         </is>
       </c>
-      <c r="AH31" t="inlineStr">
+      <c r="AN31" t="inlineStr">
         <is>
           <t>mA</t>
         </is>
       </c>
-      <c r="AI31" t="inlineStr">
+      <c r="AO31" t="inlineStr">
         <is>
           <t>Draw current from OUTP</t>
         </is>
       </c>
-      <c r="AJ31" t="inlineStr"/>
-      <c r="AK31" t="inlineStr"/>
-      <c r="AL31" t="inlineStr"/>
-      <c r="AM31" t="inlineStr"/>
-      <c r="AN31" t="inlineStr"/>
-      <c r="AO31" t="inlineStr"/>
       <c r="AP31" t="inlineStr"/>
       <c r="AQ31" t="inlineStr"/>
       <c r="AR31" t="inlineStr"/>
       <c r="AS31" t="inlineStr"/>
       <c r="AT31" t="inlineStr"/>
-      <c r="AU31" t="inlineStr">
-        <is>
-          <t>Disconnect the load</t>
-        </is>
-      </c>
+      <c r="AU31" t="inlineStr"/>
       <c r="AV31" t="inlineStr"/>
       <c r="AW31" t="inlineStr"/>
-      <c r="AX31" t="inlineStr"/>
-      <c r="AY31" t="inlineStr">
+      <c r="AX31" t="inlineStr">
+        <is>
+          <t>Disconnect the load</t>
+        </is>
+      </c>
+      <c r="AY31" t="inlineStr"/>
+      <c r="AZ31" t="inlineStr"/>
+      <c r="BA31" t="inlineStr"/>
+      <c r="BB31" t="inlineStr">
         <is>
           <t>500</t>
         </is>
       </c>
-      <c r="AZ31" t="inlineStr">
+      <c r="BC31" t="inlineStr">
         <is>
           <t>mA</t>
         </is>
       </c>
-      <c r="BA31" t="inlineStr">
+      <c r="BD31" t="inlineStr">
         <is>
           <t>Sink/Force current (disconnect the load)</t>
-        </is>
-      </c>
-      <c r="BB31" t="inlineStr"/>
-      <c r="BC31" t="inlineStr"/>
-      <c r="BD31" t="inlineStr">
-        <is>
-          <t>Disconnect the load</t>
         </is>
       </c>
       <c r="BE31" t="inlineStr"/>
       <c r="BF31" t="inlineStr"/>
-      <c r="BG31" t="inlineStr"/>
+      <c r="BG31" t="inlineStr">
+        <is>
+          <t>Disconnect the load</t>
+        </is>
+      </c>
       <c r="BH31" t="inlineStr"/>
       <c r="BI31" t="inlineStr"/>
       <c r="BJ31" t="inlineStr"/>
@@ -5583,39 +5599,39 @@
       <c r="AR32" t="inlineStr"/>
       <c r="AS32" t="inlineStr"/>
       <c r="AT32" t="inlineStr"/>
-      <c r="AU32" t="inlineStr">
-        <is>
-          <t>Disconnect the load</t>
-        </is>
-      </c>
+      <c r="AU32" t="inlineStr"/>
       <c r="AV32" t="inlineStr"/>
       <c r="AW32" t="inlineStr"/>
-      <c r="AX32" t="inlineStr"/>
-      <c r="AY32" t="inlineStr">
+      <c r="AX32" t="inlineStr">
+        <is>
+          <t>Disconnect the load</t>
+        </is>
+      </c>
+      <c r="AY32" t="inlineStr"/>
+      <c r="AZ32" t="inlineStr"/>
+      <c r="BA32" t="inlineStr"/>
+      <c r="BB32" t="inlineStr">
         <is>
           <t>500</t>
         </is>
       </c>
-      <c r="AZ32" t="inlineStr">
+      <c r="BC32" t="inlineStr">
         <is>
           <t>mA</t>
         </is>
       </c>
-      <c r="BA32" t="inlineStr">
+      <c r="BD32" t="inlineStr">
         <is>
           <t>Force/Sink current (disconnect the load)</t>
-        </is>
-      </c>
-      <c r="BB32" t="inlineStr"/>
-      <c r="BC32" t="inlineStr"/>
-      <c r="BD32" t="inlineStr">
-        <is>
-          <t>Disconnect the load</t>
         </is>
       </c>
       <c r="BE32" t="inlineStr"/>
       <c r="BF32" t="inlineStr"/>
-      <c r="BG32" t="inlineStr"/>
+      <c r="BG32" t="inlineStr">
+        <is>
+          <t>Disconnect the load</t>
+        </is>
+      </c>
       <c r="BH32" t="inlineStr"/>
       <c r="BI32" t="inlineStr"/>
       <c r="BJ32" t="inlineStr"/>
@@ -5662,17 +5678,17 @@
       <c r="R33" t="inlineStr"/>
       <c r="S33" t="inlineStr"/>
       <c r="T33" t="inlineStr"/>
-      <c r="U33" t="inlineStr">
-        <is>
-          <t>Measure frequency</t>
-        </is>
-      </c>
+      <c r="U33" t="inlineStr"/>
       <c r="V33" t="inlineStr"/>
       <c r="W33" t="inlineStr"/>
       <c r="X33" t="inlineStr"/>
       <c r="Y33" t="inlineStr"/>
       <c r="Z33" t="inlineStr"/>
-      <c r="AA33" t="inlineStr"/>
+      <c r="AA33" t="inlineStr">
+        <is>
+          <t>Measure frequency</t>
+        </is>
+      </c>
       <c r="AB33" t="inlineStr"/>
       <c r="AC33" t="inlineStr"/>
       <c r="AD33" t="inlineStr"/>
@@ -5684,14 +5700,14 @@
       <c r="AJ33" t="inlineStr"/>
       <c r="AK33" t="inlineStr"/>
       <c r="AL33" t="inlineStr"/>
-      <c r="AM33" t="inlineStr">
-        <is>
-          <t>Measure frequency</t>
-        </is>
-      </c>
+      <c r="AM33" t="inlineStr"/>
       <c r="AN33" t="inlineStr"/>
       <c r="AO33" t="inlineStr"/>
-      <c r="AP33" t="inlineStr"/>
+      <c r="AP33" t="inlineStr">
+        <is>
+          <t>Measure frequency</t>
+        </is>
+      </c>
       <c r="AQ33" t="inlineStr"/>
       <c r="AR33" t="inlineStr"/>
       <c r="AS33" t="inlineStr"/>

--- a/Aerodyne_ip_tests_summary.xlsx
+++ b/Aerodyne_ip_tests_summary.xlsx
@@ -1548,7 +1548,7 @@
       <c r="AI7" t="inlineStr"/>
       <c r="AJ7" t="inlineStr">
         <is>
-          <t>Compiled</t>
+          <t>Tested</t>
         </is>
       </c>
       <c r="AK7" t="inlineStr"/>
@@ -1569,14 +1569,14 @@
       <c r="AR7" t="inlineStr"/>
       <c r="AS7" t="inlineStr">
         <is>
-          <t>Compiled</t>
+          <t>Tested</t>
         </is>
       </c>
       <c r="AT7" t="inlineStr"/>
       <c r="AU7" t="inlineStr"/>
       <c r="AV7" t="inlineStr">
         <is>
-          <t>Compiled</t>
+          <t>Tested</t>
         </is>
       </c>
       <c r="AW7" t="inlineStr"/>
@@ -1588,32 +1588,60 @@
       </c>
       <c r="AZ7" t="inlineStr"/>
       <c r="BA7" t="inlineStr"/>
-      <c r="BB7" t="inlineStr"/>
+      <c r="BB7" t="inlineStr">
+        <is>
+          <t>Tested</t>
+        </is>
+      </c>
       <c r="BC7" t="inlineStr"/>
       <c r="BD7" t="inlineStr"/>
       <c r="BE7" t="inlineStr">
         <is>
-          <t>Compiled</t>
+          <t>Tested</t>
         </is>
       </c>
       <c r="BF7" t="inlineStr"/>
       <c r="BG7" t="inlineStr"/>
-      <c r="BH7" t="inlineStr"/>
+      <c r="BH7" t="inlineStr">
+        <is>
+          <t>Tested</t>
+        </is>
+      </c>
       <c r="BI7" t="inlineStr"/>
       <c r="BJ7" t="inlineStr"/>
-      <c r="BK7" t="inlineStr"/>
+      <c r="BK7" t="inlineStr">
+        <is>
+          <t>Tested</t>
+        </is>
+      </c>
       <c r="BL7" t="inlineStr"/>
       <c r="BM7" t="inlineStr"/>
-      <c r="BN7" t="inlineStr"/>
+      <c r="BN7" t="inlineStr">
+        <is>
+          <t>Tested</t>
+        </is>
+      </c>
       <c r="BO7" t="inlineStr"/>
       <c r="BP7" t="inlineStr"/>
-      <c r="BQ7" t="inlineStr"/>
+      <c r="BQ7" t="inlineStr">
+        <is>
+          <t>Tested</t>
+        </is>
+      </c>
       <c r="BR7" t="inlineStr"/>
       <c r="BS7" t="inlineStr"/>
-      <c r="BT7" t="inlineStr"/>
+      <c r="BT7" t="inlineStr">
+        <is>
+          <t>Tested</t>
+        </is>
+      </c>
       <c r="BU7" t="inlineStr"/>
       <c r="BV7" t="inlineStr"/>
-      <c r="BW7" t="inlineStr"/>
+      <c r="BW7" t="inlineStr">
+        <is>
+          <t>Tested</t>
+        </is>
+      </c>
       <c r="BX7" t="inlineStr"/>
       <c r="BY7" t="inlineStr"/>
     </row>
@@ -1842,7 +1870,11 @@
       </c>
       <c r="P9" t="inlineStr"/>
       <c r="Q9" t="inlineStr"/>
-      <c r="R9" t="inlineStr"/>
+      <c r="R9" t="inlineStr">
+        <is>
+          <t>DC</t>
+        </is>
+      </c>
       <c r="S9" t="inlineStr"/>
       <c r="T9" t="inlineStr"/>
       <c r="U9" t="inlineStr">

--- a/Aerodyne_ip_tests_summary.xlsx
+++ b/Aerodyne_ip_tests_summary.xlsx
@@ -1527,7 +1527,7 @@
       <c r="Z7" t="inlineStr"/>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>Compiled</t>
+          <t>Tested</t>
         </is>
       </c>
       <c r="AB7" t="inlineStr"/>
@@ -1541,7 +1541,7 @@
       <c r="AF7" t="inlineStr"/>
       <c r="AG7" t="inlineStr">
         <is>
-          <t>Compiled</t>
+          <t>Tested</t>
         </is>
       </c>
       <c r="AH7" t="inlineStr"/>
@@ -1562,7 +1562,7 @@
       <c r="AO7" t="inlineStr"/>
       <c r="AP7" t="inlineStr">
         <is>
-          <t>Compiled</t>
+          <t>Tested</t>
         </is>
       </c>
       <c r="AQ7" t="inlineStr"/>
@@ -8368,7 +8368,11 @@
         </is>
       </c>
       <c r="B7" t="inlineStr"/>
-      <c r="C7" t="inlineStr"/>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>Compiled</t>
+        </is>
+      </c>
       <c r="D7" t="inlineStr"/>
       <c r="E7" t="inlineStr"/>
       <c r="F7" t="inlineStr">
@@ -18785,7 +18789,11 @@
       <c r="O7" t="inlineStr"/>
       <c r="P7" t="inlineStr"/>
       <c r="Q7" t="inlineStr"/>
-      <c r="R7" t="inlineStr"/>
+      <c r="R7" t="inlineStr">
+        <is>
+          <t>Tested</t>
+        </is>
+      </c>
       <c r="S7" t="inlineStr"/>
       <c r="T7" t="inlineStr"/>
     </row>

--- a/Aerodyne_ip_tests_summary.xlsx
+++ b/Aerodyne_ip_tests_summary.xlsx
@@ -1555,7 +1555,7 @@
       <c r="AL7" t="inlineStr"/>
       <c r="AM7" t="inlineStr">
         <is>
-          <t>Compiled</t>
+          <t>Tested</t>
         </is>
       </c>
       <c r="AN7" t="inlineStr"/>

--- a/Aerodyne_ip_tests_summary.xlsx
+++ b/Aerodyne_ip_tests_summary.xlsx
@@ -6253,7 +6253,7 @@
       <c r="H7" t="inlineStr"/>
       <c r="I7" t="inlineStr">
         <is>
-          <t>Compiled</t>
+          <t>Tested</t>
         </is>
       </c>
       <c r="J7" t="inlineStr"/>

--- a/Aerodyne_ip_tests_summary.xlsx
+++ b/Aerodyne_ip_tests_summary.xlsx
@@ -2191,7 +2191,7 @@
       <c r="Z11" t="inlineStr"/>
       <c r="AA11" t="inlineStr">
         <is>
-          <t>9.09</t>
+          <t>4.76</t>
         </is>
       </c>
       <c r="AB11" t="inlineStr"/>

--- a/Aerodyne_ip_tests_summary.xlsx
+++ b/Aerodyne_ip_tests_summary.xlsx
@@ -2609,7 +2609,11 @@
       </c>
       <c r="AB14" t="inlineStr"/>
       <c r="AC14" t="inlineStr"/>
-      <c r="AD14" t="inlineStr"/>
+      <c r="AD14" t="inlineStr">
+        <is>
+          <t>Not @ATE</t>
+        </is>
+      </c>
       <c r="AE14" t="inlineStr"/>
       <c r="AF14" t="inlineStr"/>
       <c r="AG14" t="inlineStr"/>
@@ -2634,7 +2638,11 @@
       <c r="AV14" t="inlineStr"/>
       <c r="AW14" t="inlineStr"/>
       <c r="AX14" t="inlineStr"/>
-      <c r="AY14" t="inlineStr"/>
+      <c r="AY14" t="inlineStr">
+        <is>
+          <t>Bug / Not @ATE</t>
+        </is>
+      </c>
       <c r="AZ14" t="inlineStr"/>
       <c r="BA14" t="inlineStr"/>
       <c r="BB14" t="inlineStr"/>
@@ -6239,14 +6247,14 @@
       <c r="B7" t="inlineStr"/>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Compiled</t>
+          <t>Tested</t>
         </is>
       </c>
       <c r="D7" t="inlineStr"/>
       <c r="E7" t="inlineStr"/>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Compiled</t>
+          <t>Tested</t>
         </is>
       </c>
       <c r="G7" t="inlineStr"/>
@@ -6260,49 +6268,49 @@
       <c r="K7" t="inlineStr"/>
       <c r="L7" t="inlineStr">
         <is>
-          <t>Compiled</t>
+          <t>Tested</t>
         </is>
       </c>
       <c r="M7" t="inlineStr"/>
       <c r="N7" t="inlineStr"/>
       <c r="O7" t="inlineStr">
         <is>
-          <t>Compiled</t>
+          <t>Tested</t>
         </is>
       </c>
       <c r="P7" t="inlineStr"/>
       <c r="Q7" t="inlineStr"/>
       <c r="R7" t="inlineStr">
         <is>
-          <t>Compiled</t>
+          <t>Tested</t>
         </is>
       </c>
       <c r="S7" t="inlineStr"/>
       <c r="T7" t="inlineStr"/>
       <c r="U7" t="inlineStr">
         <is>
-          <t>Compiled</t>
+          <t>Tested</t>
         </is>
       </c>
       <c r="V7" t="inlineStr"/>
       <c r="W7" t="inlineStr"/>
       <c r="X7" t="inlineStr">
         <is>
-          <t>Compiled</t>
+          <t>Tested</t>
         </is>
       </c>
       <c r="Y7" t="inlineStr"/>
       <c r="Z7" t="inlineStr"/>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>Compiled</t>
+          <t>Tested</t>
         </is>
       </c>
       <c r="AB7" t="inlineStr"/>
       <c r="AC7" t="inlineStr"/>
       <c r="AD7" t="inlineStr">
         <is>
-          <t>Compiled</t>
+          <t>Tested</t>
         </is>
       </c>
       <c r="AE7" t="inlineStr"/>
@@ -8370,21 +8378,21 @@
       <c r="B7" t="inlineStr"/>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Compiled</t>
+          <t>Tested</t>
         </is>
       </c>
       <c r="D7" t="inlineStr"/>
       <c r="E7" t="inlineStr"/>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Compiled</t>
+          <t>Tested</t>
         </is>
       </c>
       <c r="G7" t="inlineStr"/>
       <c r="H7" t="inlineStr"/>
       <c r="I7" t="inlineStr">
         <is>
-          <t>Compiled</t>
+          <t>Tested</t>
         </is>
       </c>
       <c r="J7" t="inlineStr"/>
@@ -9520,28 +9528,28 @@
       <c r="B7" t="inlineStr"/>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Compiled</t>
+          <t>Tested</t>
         </is>
       </c>
       <c r="D7" t="inlineStr"/>
       <c r="E7" t="inlineStr"/>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Compiled</t>
+          <t>Tested</t>
         </is>
       </c>
       <c r="G7" t="inlineStr"/>
       <c r="H7" t="inlineStr"/>
       <c r="I7" t="inlineStr">
         <is>
-          <t>Compiled</t>
+          <t>Tested</t>
         </is>
       </c>
       <c r="J7" t="inlineStr"/>
       <c r="K7" t="inlineStr"/>
       <c r="L7" t="inlineStr">
         <is>
-          <t>Compiled</t>
+          <t>Tested</t>
         </is>
       </c>
       <c r="M7" t="inlineStr"/>
@@ -12321,91 +12329,91 @@
       <c r="B7" t="inlineStr"/>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Compiled</t>
+          <t>Tested</t>
         </is>
       </c>
       <c r="D7" t="inlineStr"/>
       <c r="E7" t="inlineStr"/>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Compiled</t>
+          <t>Tested</t>
         </is>
       </c>
       <c r="G7" t="inlineStr"/>
       <c r="H7" t="inlineStr"/>
       <c r="I7" t="inlineStr">
         <is>
-          <t>Compiled</t>
+          <t>Tested</t>
         </is>
       </c>
       <c r="J7" t="inlineStr"/>
       <c r="K7" t="inlineStr"/>
       <c r="L7" t="inlineStr">
         <is>
-          <t>Compiled</t>
+          <t>Tested</t>
         </is>
       </c>
       <c r="M7" t="inlineStr"/>
       <c r="N7" t="inlineStr"/>
       <c r="O7" t="inlineStr">
         <is>
-          <t>Compiled</t>
+          <t>Tested</t>
         </is>
       </c>
       <c r="P7" t="inlineStr"/>
       <c r="Q7" t="inlineStr"/>
       <c r="R7" t="inlineStr">
         <is>
-          <t>Compiled</t>
+          <t>Tested</t>
         </is>
       </c>
       <c r="S7" t="inlineStr"/>
       <c r="T7" t="inlineStr"/>
       <c r="U7" t="inlineStr">
         <is>
-          <t>Compiled</t>
+          <t>Tested</t>
         </is>
       </c>
       <c r="V7" t="inlineStr"/>
       <c r="W7" t="inlineStr"/>
       <c r="X7" t="inlineStr">
         <is>
-          <t>Compiled</t>
+          <t>Tested</t>
         </is>
       </c>
       <c r="Y7" t="inlineStr"/>
       <c r="Z7" t="inlineStr"/>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>Compiled</t>
+          <t>Tested</t>
         </is>
       </c>
       <c r="AB7" t="inlineStr"/>
       <c r="AC7" t="inlineStr"/>
       <c r="AD7" t="inlineStr">
         <is>
-          <t>Compiled</t>
+          <t>Tested</t>
         </is>
       </c>
       <c r="AE7" t="inlineStr"/>
       <c r="AF7" t="inlineStr"/>
       <c r="AG7" t="inlineStr">
         <is>
-          <t>Compiled</t>
+          <t>Tested</t>
         </is>
       </c>
       <c r="AH7" t="inlineStr"/>
       <c r="AI7" t="inlineStr"/>
       <c r="AJ7" t="inlineStr">
         <is>
-          <t>Compiled</t>
+          <t>Tested</t>
         </is>
       </c>
       <c r="AK7" t="inlineStr"/>
       <c r="AL7" t="inlineStr"/>
       <c r="AM7" t="inlineStr">
         <is>
-          <t>Compiled</t>
+          <t>Tested</t>
         </is>
       </c>
       <c r="AN7" t="inlineStr"/>
@@ -12447,7 +12455,7 @@
       <c r="BD7" t="inlineStr"/>
       <c r="BE7" t="inlineStr">
         <is>
-          <t>Compiled</t>
+          <t>Tested</t>
         </is>
       </c>
       <c r="BF7" t="inlineStr"/>
@@ -12468,40 +12476,44 @@
       <c r="BM7" t="inlineStr"/>
       <c r="BN7" t="inlineStr">
         <is>
-          <t>Compiled</t>
+          <t>Tested</t>
         </is>
       </c>
       <c r="BO7" t="inlineStr"/>
       <c r="BP7" t="inlineStr"/>
       <c r="BQ7" t="inlineStr">
         <is>
-          <t>Compiled</t>
+          <t>Tested</t>
         </is>
       </c>
       <c r="BR7" t="inlineStr"/>
       <c r="BS7" t="inlineStr"/>
       <c r="BT7" t="inlineStr">
         <is>
-          <t>Compiled</t>
+          <t>Tested</t>
         </is>
       </c>
       <c r="BU7" t="inlineStr"/>
       <c r="BV7" t="inlineStr"/>
       <c r="BW7" t="inlineStr">
         <is>
-          <t>Compiled</t>
+          <t>Tested</t>
         </is>
       </c>
       <c r="BX7" t="inlineStr"/>
       <c r="BY7" t="inlineStr"/>
       <c r="BZ7" t="inlineStr">
         <is>
-          <t>Compiled</t>
+          <t>Tested</t>
         </is>
       </c>
       <c r="CA7" t="inlineStr"/>
       <c r="CB7" t="inlineStr"/>
-      <c r="CC7" t="inlineStr"/>
+      <c r="CC7" t="inlineStr">
+        <is>
+          <t>Tested</t>
+        </is>
+      </c>
       <c r="CD7" t="inlineStr"/>
       <c r="CE7" t="inlineStr"/>
     </row>
@@ -13592,7 +13604,7 @@
       <c r="B14" t="inlineStr"/>
       <c r="C14" t="inlineStr">
         <is>
-          <t>10nA precision required</t>
+          <t>Do not Perform @ ATE</t>
         </is>
       </c>
       <c r="D14" t="inlineStr"/>
@@ -17825,16 +17837,32 @@
         </is>
       </c>
       <c r="B14" t="inlineStr"/>
-      <c r="C14" t="inlineStr"/>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>Bug / Not @ATE</t>
+        </is>
+      </c>
       <c r="D14" t="inlineStr"/>
       <c r="E14" t="inlineStr"/>
-      <c r="F14" t="inlineStr"/>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>Bug / Not @ATE</t>
+        </is>
+      </c>
       <c r="G14" t="inlineStr"/>
       <c r="H14" t="inlineStr"/>
-      <c r="I14" t="inlineStr"/>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>Bug / Not @ATE</t>
+        </is>
+      </c>
       <c r="J14" t="inlineStr"/>
       <c r="K14" t="inlineStr"/>
-      <c r="L14" t="inlineStr"/>
+      <c r="L14" t="inlineStr">
+        <is>
+          <t>Bug / Not @ATE</t>
+        </is>
+      </c>
       <c r="M14" t="inlineStr"/>
       <c r="N14" t="inlineStr"/>
     </row>
@@ -18484,7 +18512,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:T34"/>
+  <dimension ref="A1:Z34"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -18532,6 +18560,20 @@
       </c>
       <c r="S1" t="inlineStr"/>
       <c r="T1" t="inlineStr"/>
+      <c r="U1" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="V1" t="inlineStr"/>
+      <c r="W1" t="inlineStr"/>
+      <c r="X1" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="Y1" t="inlineStr"/>
+      <c r="Z1" t="inlineStr"/>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr"/>
@@ -18578,6 +18620,20 @@
       </c>
       <c r="S2" t="inlineStr"/>
       <c r="T2" t="inlineStr"/>
+      <c r="U2" t="inlineStr">
+        <is>
+          <t>Parameters</t>
+        </is>
+      </c>
+      <c r="V2" t="inlineStr"/>
+      <c r="W2" t="inlineStr"/>
+      <c r="X2" t="inlineStr">
+        <is>
+          <t>Parameters</t>
+        </is>
+      </c>
+      <c r="Y2" t="inlineStr"/>
+      <c r="Z2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -18616,6 +18672,16 @@
       </c>
       <c r="S3" t="inlineStr"/>
       <c r="T3" t="inlineStr"/>
+      <c r="U3" t="n">
+        <v>84</v>
+      </c>
+      <c r="V3" t="inlineStr"/>
+      <c r="W3" t="inlineStr"/>
+      <c r="X3" t="n">
+        <v>85</v>
+      </c>
+      <c r="Y3" t="inlineStr"/>
+      <c r="Z3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -18666,6 +18732,20 @@
       </c>
       <c r="S4" t="inlineStr"/>
       <c r="T4" t="inlineStr"/>
+      <c r="U4" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="V4" t="inlineStr"/>
+      <c r="W4" t="inlineStr"/>
+      <c r="X4" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="Y4" t="inlineStr"/>
+      <c r="Z4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -18716,6 +18796,20 @@
       </c>
       <c r="S5" t="inlineStr"/>
       <c r="T5" t="inlineStr"/>
+      <c r="U5" t="inlineStr">
+        <is>
+          <t>Digital</t>
+        </is>
+      </c>
+      <c r="V5" t="inlineStr"/>
+      <c r="W5" t="inlineStr"/>
+      <c r="X5" t="inlineStr">
+        <is>
+          <t>Digital</t>
+        </is>
+      </c>
+      <c r="Y5" t="inlineStr"/>
+      <c r="Z5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -18766,6 +18860,20 @@
       </c>
       <c r="S6" t="inlineStr"/>
       <c r="T6" t="inlineStr"/>
+      <c r="U6" t="inlineStr">
+        <is>
+          <t>V-randomizer SCAN</t>
+        </is>
+      </c>
+      <c r="V6" t="inlineStr"/>
+      <c r="W6" t="inlineStr"/>
+      <c r="X6" t="inlineStr">
+        <is>
+          <t>I-randomizer SCAN</t>
+        </is>
+      </c>
+      <c r="Y6" t="inlineStr"/>
+      <c r="Z6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -18796,6 +18904,12 @@
       </c>
       <c r="S7" t="inlineStr"/>
       <c r="T7" t="inlineStr"/>
+      <c r="U7" t="inlineStr"/>
+      <c r="V7" t="inlineStr"/>
+      <c r="W7" t="inlineStr"/>
+      <c r="X7" t="inlineStr"/>
+      <c r="Y7" t="inlineStr"/>
+      <c r="Z7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -18822,6 +18936,12 @@
       <c r="R8" t="inlineStr"/>
       <c r="S8" t="inlineStr"/>
       <c r="T8" t="inlineStr"/>
+      <c r="U8" t="inlineStr"/>
+      <c r="V8" t="inlineStr"/>
+      <c r="W8" t="inlineStr"/>
+      <c r="X8" t="inlineStr"/>
+      <c r="Y8" t="inlineStr"/>
+      <c r="Z8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -18848,6 +18968,12 @@
       <c r="R9" t="inlineStr"/>
       <c r="S9" t="inlineStr"/>
       <c r="T9" t="inlineStr"/>
+      <c r="U9" t="inlineStr"/>
+      <c r="V9" t="inlineStr"/>
+      <c r="W9" t="inlineStr"/>
+      <c r="X9" t="inlineStr"/>
+      <c r="Y9" t="inlineStr"/>
+      <c r="Z9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -18874,6 +19000,12 @@
       <c r="R10" t="inlineStr"/>
       <c r="S10" t="inlineStr"/>
       <c r="T10" t="inlineStr"/>
+      <c r="U10" t="inlineStr"/>
+      <c r="V10" t="inlineStr"/>
+      <c r="W10" t="inlineStr"/>
+      <c r="X10" t="inlineStr"/>
+      <c r="Y10" t="inlineStr"/>
+      <c r="Z10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -18900,6 +19032,12 @@
       <c r="R11" t="inlineStr"/>
       <c r="S11" t="inlineStr"/>
       <c r="T11" t="inlineStr"/>
+      <c r="U11" t="inlineStr"/>
+      <c r="V11" t="inlineStr"/>
+      <c r="W11" t="inlineStr"/>
+      <c r="X11" t="inlineStr"/>
+      <c r="Y11" t="inlineStr"/>
+      <c r="Z11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -18926,6 +19064,12 @@
       <c r="R12" t="inlineStr"/>
       <c r="S12" t="inlineStr"/>
       <c r="T12" t="inlineStr"/>
+      <c r="U12" t="inlineStr"/>
+      <c r="V12" t="inlineStr"/>
+      <c r="W12" t="inlineStr"/>
+      <c r="X12" t="inlineStr"/>
+      <c r="Y12" t="inlineStr"/>
+      <c r="Z12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -18952,6 +19096,12 @@
       <c r="R13" t="inlineStr"/>
       <c r="S13" t="inlineStr"/>
       <c r="T13" t="inlineStr"/>
+      <c r="U13" t="inlineStr"/>
+      <c r="V13" t="inlineStr"/>
+      <c r="W13" t="inlineStr"/>
+      <c r="X13" t="inlineStr"/>
+      <c r="Y13" t="inlineStr"/>
+      <c r="Z13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -18978,6 +19128,12 @@
       <c r="R14" t="inlineStr"/>
       <c r="S14" t="inlineStr"/>
       <c r="T14" t="inlineStr"/>
+      <c r="U14" t="inlineStr"/>
+      <c r="V14" t="inlineStr"/>
+      <c r="W14" t="inlineStr"/>
+      <c r="X14" t="inlineStr"/>
+      <c r="Y14" t="inlineStr"/>
+      <c r="Z14" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
@@ -19083,6 +19239,36 @@
         </is>
       </c>
       <c r="T17" t="inlineStr">
+        <is>
+          <t>Pin requirements</t>
+        </is>
+      </c>
+      <c r="U17" t="inlineStr">
+        <is>
+          <t>Value</t>
+        </is>
+      </c>
+      <c r="V17" t="inlineStr">
+        <is>
+          <t>Unit</t>
+        </is>
+      </c>
+      <c r="W17" t="inlineStr">
+        <is>
+          <t>Pin requirements</t>
+        </is>
+      </c>
+      <c r="X17" t="inlineStr">
+        <is>
+          <t>Value</t>
+        </is>
+      </c>
+      <c r="Y17" t="inlineStr">
+        <is>
+          <t>Unit</t>
+        </is>
+      </c>
+      <c r="Z17" t="inlineStr">
         <is>
           <t>Pin requirements</t>
         </is>
@@ -19113,6 +19299,12 @@
       <c r="R18" t="inlineStr"/>
       <c r="S18" t="inlineStr"/>
       <c r="T18" t="inlineStr"/>
+      <c r="U18" t="inlineStr"/>
+      <c r="V18" t="inlineStr"/>
+      <c r="W18" t="inlineStr"/>
+      <c r="X18" t="inlineStr"/>
+      <c r="Y18" t="inlineStr"/>
+      <c r="Z18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" t="n">
@@ -19145,6 +19337,12 @@
       <c r="R19" t="inlineStr"/>
       <c r="S19" t="inlineStr"/>
       <c r="T19" t="inlineStr"/>
+      <c r="U19" t="inlineStr"/>
+      <c r="V19" t="inlineStr"/>
+      <c r="W19" t="inlineStr"/>
+      <c r="X19" t="inlineStr"/>
+      <c r="Y19" t="inlineStr"/>
+      <c r="Z19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" t="n">
@@ -19177,6 +19375,12 @@
       <c r="R20" t="inlineStr"/>
       <c r="S20" t="inlineStr"/>
       <c r="T20" t="inlineStr"/>
+      <c r="U20" t="inlineStr"/>
+      <c r="V20" t="inlineStr"/>
+      <c r="W20" t="inlineStr"/>
+      <c r="X20" t="inlineStr"/>
+      <c r="Y20" t="inlineStr"/>
+      <c r="Z20" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" t="n">
@@ -19209,6 +19413,12 @@
       <c r="R21" t="inlineStr"/>
       <c r="S21" t="inlineStr"/>
       <c r="T21" t="inlineStr"/>
+      <c r="U21" t="inlineStr"/>
+      <c r="V21" t="inlineStr"/>
+      <c r="W21" t="inlineStr"/>
+      <c r="X21" t="inlineStr"/>
+      <c r="Y21" t="inlineStr"/>
+      <c r="Z21" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" t="n">
@@ -19241,6 +19451,12 @@
       <c r="R22" t="inlineStr"/>
       <c r="S22" t="inlineStr"/>
       <c r="T22" t="inlineStr"/>
+      <c r="U22" t="inlineStr"/>
+      <c r="V22" t="inlineStr"/>
+      <c r="W22" t="inlineStr"/>
+      <c r="X22" t="inlineStr"/>
+      <c r="Y22" t="inlineStr"/>
+      <c r="Z22" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" t="n">
@@ -19285,6 +19501,12 @@
         </is>
       </c>
       <c r="T23" t="inlineStr"/>
+      <c r="U23" t="inlineStr"/>
+      <c r="V23" t="inlineStr"/>
+      <c r="W23" t="inlineStr"/>
+      <c r="X23" t="inlineStr"/>
+      <c r="Y23" t="inlineStr"/>
+      <c r="Z23" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" t="n">
@@ -19327,6 +19549,12 @@
         </is>
       </c>
       <c r="T24" t="inlineStr"/>
+      <c r="U24" t="inlineStr"/>
+      <c r="V24" t="inlineStr"/>
+      <c r="W24" t="inlineStr"/>
+      <c r="X24" t="inlineStr"/>
+      <c r="Y24" t="inlineStr"/>
+      <c r="Z24" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" t="n">
@@ -19355,6 +19583,12 @@
       <c r="R25" t="inlineStr"/>
       <c r="S25" t="inlineStr"/>
       <c r="T25" t="inlineStr"/>
+      <c r="U25" t="inlineStr"/>
+      <c r="V25" t="inlineStr"/>
+      <c r="W25" t="inlineStr"/>
+      <c r="X25" t="inlineStr"/>
+      <c r="Y25" t="inlineStr"/>
+      <c r="Z25" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="A26" t="n">
@@ -19395,6 +19629,12 @@
       <c r="R26" t="inlineStr"/>
       <c r="S26" t="inlineStr"/>
       <c r="T26" t="inlineStr"/>
+      <c r="U26" t="inlineStr"/>
+      <c r="V26" t="inlineStr"/>
+      <c r="W26" t="inlineStr"/>
+      <c r="X26" t="inlineStr"/>
+      <c r="Y26" t="inlineStr"/>
+      <c r="Z26" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" t="n">
@@ -19435,6 +19675,12 @@
         </is>
       </c>
       <c r="T27" t="inlineStr"/>
+      <c r="U27" t="inlineStr"/>
+      <c r="V27" t="inlineStr"/>
+      <c r="W27" t="inlineStr"/>
+      <c r="X27" t="inlineStr"/>
+      <c r="Y27" t="inlineStr"/>
+      <c r="Z27" t="inlineStr"/>
     </row>
     <row r="28">
       <c r="A28" t="n">
@@ -19475,6 +19721,12 @@
         </is>
       </c>
       <c r="T28" t="inlineStr"/>
+      <c r="U28" t="inlineStr"/>
+      <c r="V28" t="inlineStr"/>
+      <c r="W28" t="inlineStr"/>
+      <c r="X28" t="inlineStr"/>
+      <c r="Y28" t="inlineStr"/>
+      <c r="Z28" t="inlineStr"/>
     </row>
     <row r="29">
       <c r="A29" t="n">
@@ -19507,6 +19759,12 @@
       <c r="R29" t="inlineStr"/>
       <c r="S29" t="inlineStr"/>
       <c r="T29" t="inlineStr"/>
+      <c r="U29" t="inlineStr"/>
+      <c r="V29" t="inlineStr"/>
+      <c r="W29" t="inlineStr"/>
+      <c r="X29" t="inlineStr"/>
+      <c r="Y29" t="inlineStr"/>
+      <c r="Z29" t="inlineStr"/>
     </row>
     <row r="30">
       <c r="A30" t="n">
@@ -19535,6 +19793,12 @@
       <c r="R30" t="inlineStr"/>
       <c r="S30" t="inlineStr"/>
       <c r="T30" t="inlineStr"/>
+      <c r="U30" t="inlineStr"/>
+      <c r="V30" t="inlineStr"/>
+      <c r="W30" t="inlineStr"/>
+      <c r="X30" t="inlineStr"/>
+      <c r="Y30" t="inlineStr"/>
+      <c r="Z30" t="inlineStr"/>
     </row>
     <row r="31">
       <c r="A31" t="n">
@@ -19563,6 +19827,12 @@
       <c r="R31" t="inlineStr"/>
       <c r="S31" t="inlineStr"/>
       <c r="T31" t="inlineStr"/>
+      <c r="U31" t="inlineStr"/>
+      <c r="V31" t="inlineStr"/>
+      <c r="W31" t="inlineStr"/>
+      <c r="X31" t="inlineStr"/>
+      <c r="Y31" t="inlineStr"/>
+      <c r="Z31" t="inlineStr"/>
     </row>
     <row r="32">
       <c r="A32" t="n">
@@ -19591,6 +19861,12 @@
       <c r="R32" t="inlineStr"/>
       <c r="S32" t="inlineStr"/>
       <c r="T32" t="inlineStr"/>
+      <c r="U32" t="inlineStr"/>
+      <c r="V32" t="inlineStr"/>
+      <c r="W32" t="inlineStr"/>
+      <c r="X32" t="inlineStr"/>
+      <c r="Y32" t="inlineStr"/>
+      <c r="Z32" t="inlineStr"/>
     </row>
     <row r="33">
       <c r="A33" t="n">
@@ -19619,6 +19895,12 @@
       <c r="R33" t="inlineStr"/>
       <c r="S33" t="inlineStr"/>
       <c r="T33" t="inlineStr"/>
+      <c r="U33" t="inlineStr"/>
+      <c r="V33" t="inlineStr"/>
+      <c r="W33" t="inlineStr"/>
+      <c r="X33" t="inlineStr"/>
+      <c r="Y33" t="inlineStr"/>
+      <c r="Z33" t="inlineStr"/>
     </row>
     <row r="34">
       <c r="A34" t="n">
@@ -19651,6 +19933,12 @@
       <c r="R34" t="inlineStr"/>
       <c r="S34" t="inlineStr"/>
       <c r="T34" t="inlineStr"/>
+      <c r="U34" t="inlineStr"/>
+      <c r="V34" t="inlineStr"/>
+      <c r="W34" t="inlineStr"/>
+      <c r="X34" t="inlineStr"/>
+      <c r="Y34" t="inlineStr"/>
+      <c r="Z34" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/Aerodyne_ip_tests_summary.xlsx
+++ b/Aerodyne_ip_tests_summary.xlsx
@@ -14,6 +14,7 @@
     <sheet name="ClassD" sheetId="5" state="visible" r:id="rId5"/>
     <sheet name="GPADC" sheetId="6" state="visible" r:id="rId6"/>
     <sheet name="Digital" sheetId="7" state="visible" r:id="rId7"/>
+    <sheet name="Thermal" sheetId="8" state="visible" r:id="rId8"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -19943,4 +19944,313 @@
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:H18"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="inlineStr"/>
+      <c r="B1" t="inlineStr"/>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr"/>
+      <c r="E1" t="inlineStr"/>
+      <c r="F1" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="G1" t="inlineStr"/>
+      <c r="H1" t="inlineStr"/>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr"/>
+      <c r="B2" t="inlineStr"/>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>Parameters</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr"/>
+      <c r="E2" t="inlineStr"/>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>Parameters</t>
+        </is>
+      </c>
+      <c r="G2" t="inlineStr"/>
+      <c r="H2" t="inlineStr"/>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>slno</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr"/>
+      <c r="C3" t="n">
+        <v>86</v>
+      </c>
+      <c r="D3" t="inlineStr"/>
+      <c r="E3" t="inlineStr"/>
+      <c r="F3" t="n">
+        <v>87</v>
+      </c>
+      <c r="G3" t="inlineStr"/>
+      <c r="H3" t="inlineStr"/>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>priority</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr"/>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr"/>
+      <c r="E4" t="inlineStr"/>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr"/>
+      <c r="H4" t="inlineStr"/>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>ipName</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr"/>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>Thermal</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr"/>
+      <c r="E5" t="inlineStr"/>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Thermal</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr"/>
+      <c r="H5" t="inlineStr"/>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>testName</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr"/>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>Ana_Reference_th</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr"/>
+      <c r="E6" t="inlineStr"/>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>Ana_PLL_th</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr"/>
+      <c r="H6" t="inlineStr"/>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>stage</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr"/>
+      <c r="C7" t="inlineStr"/>
+      <c r="D7" t="inlineStr"/>
+      <c r="E7" t="inlineStr"/>
+      <c r="F7" t="inlineStr"/>
+      <c r="G7" t="inlineStr"/>
+      <c r="H7" t="inlineStr"/>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>signalName</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr"/>
+      <c r="C8" t="inlineStr"/>
+      <c r="D8" t="inlineStr"/>
+      <c r="E8" t="inlineStr"/>
+      <c r="F8" t="inlineStr"/>
+      <c r="G8" t="inlineStr"/>
+      <c r="H8" t="inlineStr"/>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>signalType</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr"/>
+      <c r="C9" t="inlineStr"/>
+      <c r="D9" t="inlineStr"/>
+      <c r="E9" t="inlineStr"/>
+      <c r="F9" t="inlineStr"/>
+      <c r="G9" t="inlineStr"/>
+      <c r="H9" t="inlineStr"/>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>minLimit</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr"/>
+      <c r="C10" t="inlineStr"/>
+      <c r="D10" t="inlineStr"/>
+      <c r="E10" t="inlineStr"/>
+      <c r="F10" t="inlineStr"/>
+      <c r="G10" t="inlineStr"/>
+      <c r="H10" t="inlineStr"/>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>typical</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr"/>
+      <c r="C11" t="inlineStr"/>
+      <c r="D11" t="inlineStr"/>
+      <c r="E11" t="inlineStr"/>
+      <c r="F11" t="inlineStr"/>
+      <c r="G11" t="inlineStr"/>
+      <c r="H11" t="inlineStr"/>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>maxLimit</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr"/>
+      <c r="C12" t="inlineStr"/>
+      <c r="D12" t="inlineStr"/>
+      <c r="E12" t="inlineStr"/>
+      <c r="F12" t="inlineStr"/>
+      <c r="G12" t="inlineStr"/>
+      <c r="H12" t="inlineStr"/>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>unit</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr"/>
+      <c r="C13" t="inlineStr"/>
+      <c r="D13" t="inlineStr"/>
+      <c r="E13" t="inlineStr"/>
+      <c r="F13" t="inlineStr"/>
+      <c r="G13" t="inlineStr"/>
+      <c r="H13" t="inlineStr"/>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>testRequirements</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr"/>
+      <c r="C14" t="inlineStr"/>
+      <c r="D14" t="inlineStr"/>
+      <c r="E14" t="inlineStr"/>
+      <c r="F14" t="inlineStr"/>
+      <c r="G14" t="inlineStr"/>
+      <c r="H14" t="inlineStr"/>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>Pin Requirements</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>Pin Number</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>Name</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>Value</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>Unit</t>
+        </is>
+      </c>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t>Pin requirements</t>
+        </is>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>Value</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>Unit</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>Pin requirements</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr"/>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>IOCLK1</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr"/>
+      <c r="D18" t="inlineStr"/>
+      <c r="E18" t="inlineStr"/>
+      <c r="F18" t="inlineStr"/>
+      <c r="G18" t="inlineStr"/>
+      <c r="H18" t="inlineStr"/>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
 </file>
--- a/Aerodyne_ip_tests_summary.xlsx
+++ b/Aerodyne_ip_tests_summary.xlsx
@@ -19952,7 +19952,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H18"/>
+  <dimension ref="A1:Q18"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -19972,6 +19972,27 @@
       </c>
       <c r="G1" t="inlineStr"/>
       <c r="H1" t="inlineStr"/>
+      <c r="I1" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="J1" t="inlineStr"/>
+      <c r="K1" t="inlineStr"/>
+      <c r="L1" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="M1" t="inlineStr"/>
+      <c r="N1" t="inlineStr"/>
+      <c r="O1" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="P1" t="inlineStr"/>
+      <c r="Q1" t="inlineStr"/>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr"/>
@@ -19990,6 +20011,27 @@
       </c>
       <c r="G2" t="inlineStr"/>
       <c r="H2" t="inlineStr"/>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>Parameters</t>
+        </is>
+      </c>
+      <c r="J2" t="inlineStr"/>
+      <c r="K2" t="inlineStr"/>
+      <c r="L2" t="inlineStr">
+        <is>
+          <t>Parameters</t>
+        </is>
+      </c>
+      <c r="M2" t="inlineStr"/>
+      <c r="N2" t="inlineStr"/>
+      <c r="O2" t="inlineStr">
+        <is>
+          <t>Parameters</t>
+        </is>
+      </c>
+      <c r="P2" t="inlineStr"/>
+      <c r="Q2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -20008,6 +20050,21 @@
       </c>
       <c r="G3" t="inlineStr"/>
       <c r="H3" t="inlineStr"/>
+      <c r="I3" t="n">
+        <v>88</v>
+      </c>
+      <c r="J3" t="inlineStr"/>
+      <c r="K3" t="inlineStr"/>
+      <c r="L3" t="n">
+        <v>89</v>
+      </c>
+      <c r="M3" t="inlineStr"/>
+      <c r="N3" t="inlineStr"/>
+      <c r="O3" t="n">
+        <v>90</v>
+      </c>
+      <c r="P3" t="inlineStr"/>
+      <c r="Q3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -20030,6 +20087,27 @@
       </c>
       <c r="G4" t="inlineStr"/>
       <c r="H4" t="inlineStr"/>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr"/>
+      <c r="K4" t="inlineStr"/>
+      <c r="L4" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="M4" t="inlineStr"/>
+      <c r="N4" t="inlineStr"/>
+      <c r="O4" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="P4" t="inlineStr"/>
+      <c r="Q4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -20052,6 +20130,27 @@
       </c>
       <c r="G5" t="inlineStr"/>
       <c r="H5" t="inlineStr"/>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>Thermal</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr"/>
+      <c r="K5" t="inlineStr"/>
+      <c r="L5" t="inlineStr">
+        <is>
+          <t>Thermal</t>
+        </is>
+      </c>
+      <c r="M5" t="inlineStr"/>
+      <c r="N5" t="inlineStr"/>
+      <c r="O5" t="inlineStr">
+        <is>
+          <t>Thermal</t>
+        </is>
+      </c>
+      <c r="P5" t="inlineStr"/>
+      <c r="Q5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -20074,6 +20173,27 @@
       </c>
       <c r="G6" t="inlineStr"/>
       <c r="H6" t="inlineStr"/>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>Ana_CLD_DAC_LPF</t>
+        </is>
+      </c>
+      <c r="J6" t="inlineStr"/>
+      <c r="K6" t="inlineStr"/>
+      <c r="L6" t="inlineStr">
+        <is>
+          <t>Ana_CLD_Driver</t>
+        </is>
+      </c>
+      <c r="M6" t="inlineStr"/>
+      <c r="N6" t="inlineStr"/>
+      <c r="O6" t="inlineStr">
+        <is>
+          <t>Ana_CLD_PWM</t>
+        </is>
+      </c>
+      <c r="P6" t="inlineStr"/>
+      <c r="Q6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -20088,6 +20208,15 @@
       <c r="F7" t="inlineStr"/>
       <c r="G7" t="inlineStr"/>
       <c r="H7" t="inlineStr"/>
+      <c r="I7" t="inlineStr"/>
+      <c r="J7" t="inlineStr"/>
+      <c r="K7" t="inlineStr"/>
+      <c r="L7" t="inlineStr"/>
+      <c r="M7" t="inlineStr"/>
+      <c r="N7" t="inlineStr"/>
+      <c r="O7" t="inlineStr"/>
+      <c r="P7" t="inlineStr"/>
+      <c r="Q7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -20102,6 +20231,15 @@
       <c r="F8" t="inlineStr"/>
       <c r="G8" t="inlineStr"/>
       <c r="H8" t="inlineStr"/>
+      <c r="I8" t="inlineStr"/>
+      <c r="J8" t="inlineStr"/>
+      <c r="K8" t="inlineStr"/>
+      <c r="L8" t="inlineStr"/>
+      <c r="M8" t="inlineStr"/>
+      <c r="N8" t="inlineStr"/>
+      <c r="O8" t="inlineStr"/>
+      <c r="P8" t="inlineStr"/>
+      <c r="Q8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -20116,6 +20254,15 @@
       <c r="F9" t="inlineStr"/>
       <c r="G9" t="inlineStr"/>
       <c r="H9" t="inlineStr"/>
+      <c r="I9" t="inlineStr"/>
+      <c r="J9" t="inlineStr"/>
+      <c r="K9" t="inlineStr"/>
+      <c r="L9" t="inlineStr"/>
+      <c r="M9" t="inlineStr"/>
+      <c r="N9" t="inlineStr"/>
+      <c r="O9" t="inlineStr"/>
+      <c r="P9" t="inlineStr"/>
+      <c r="Q9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -20130,6 +20277,15 @@
       <c r="F10" t="inlineStr"/>
       <c r="G10" t="inlineStr"/>
       <c r="H10" t="inlineStr"/>
+      <c r="I10" t="inlineStr"/>
+      <c r="J10" t="inlineStr"/>
+      <c r="K10" t="inlineStr"/>
+      <c r="L10" t="inlineStr"/>
+      <c r="M10" t="inlineStr"/>
+      <c r="N10" t="inlineStr"/>
+      <c r="O10" t="inlineStr"/>
+      <c r="P10" t="inlineStr"/>
+      <c r="Q10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -20144,6 +20300,15 @@
       <c r="F11" t="inlineStr"/>
       <c r="G11" t="inlineStr"/>
       <c r="H11" t="inlineStr"/>
+      <c r="I11" t="inlineStr"/>
+      <c r="J11" t="inlineStr"/>
+      <c r="K11" t="inlineStr"/>
+      <c r="L11" t="inlineStr"/>
+      <c r="M11" t="inlineStr"/>
+      <c r="N11" t="inlineStr"/>
+      <c r="O11" t="inlineStr"/>
+      <c r="P11" t="inlineStr"/>
+      <c r="Q11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -20158,6 +20323,15 @@
       <c r="F12" t="inlineStr"/>
       <c r="G12" t="inlineStr"/>
       <c r="H12" t="inlineStr"/>
+      <c r="I12" t="inlineStr"/>
+      <c r="J12" t="inlineStr"/>
+      <c r="K12" t="inlineStr"/>
+      <c r="L12" t="inlineStr"/>
+      <c r="M12" t="inlineStr"/>
+      <c r="N12" t="inlineStr"/>
+      <c r="O12" t="inlineStr"/>
+      <c r="P12" t="inlineStr"/>
+      <c r="Q12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -20172,6 +20346,15 @@
       <c r="F13" t="inlineStr"/>
       <c r="G13" t="inlineStr"/>
       <c r="H13" t="inlineStr"/>
+      <c r="I13" t="inlineStr"/>
+      <c r="J13" t="inlineStr"/>
+      <c r="K13" t="inlineStr"/>
+      <c r="L13" t="inlineStr"/>
+      <c r="M13" t="inlineStr"/>
+      <c r="N13" t="inlineStr"/>
+      <c r="O13" t="inlineStr"/>
+      <c r="P13" t="inlineStr"/>
+      <c r="Q13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -20186,6 +20369,15 @@
       <c r="F14" t="inlineStr"/>
       <c r="G14" t="inlineStr"/>
       <c r="H14" t="inlineStr"/>
+      <c r="I14" t="inlineStr"/>
+      <c r="J14" t="inlineStr"/>
+      <c r="K14" t="inlineStr"/>
+      <c r="L14" t="inlineStr"/>
+      <c r="M14" t="inlineStr"/>
+      <c r="N14" t="inlineStr"/>
+      <c r="O14" t="inlineStr"/>
+      <c r="P14" t="inlineStr"/>
+      <c r="Q14" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
@@ -20231,6 +20423,51 @@
         </is>
       </c>
       <c r="H17" t="inlineStr">
+        <is>
+          <t>Pin requirements</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr">
+        <is>
+          <t>Value</t>
+        </is>
+      </c>
+      <c r="J17" t="inlineStr">
+        <is>
+          <t>Unit</t>
+        </is>
+      </c>
+      <c r="K17" t="inlineStr">
+        <is>
+          <t>Pin requirements</t>
+        </is>
+      </c>
+      <c r="L17" t="inlineStr">
+        <is>
+          <t>Value</t>
+        </is>
+      </c>
+      <c r="M17" t="inlineStr">
+        <is>
+          <t>Unit</t>
+        </is>
+      </c>
+      <c r="N17" t="inlineStr">
+        <is>
+          <t>Pin requirements</t>
+        </is>
+      </c>
+      <c r="O17" t="inlineStr">
+        <is>
+          <t>Value</t>
+        </is>
+      </c>
+      <c r="P17" t="inlineStr">
+        <is>
+          <t>Unit</t>
+        </is>
+      </c>
+      <c r="Q17" t="inlineStr">
         <is>
           <t>Pin requirements</t>
         </is>
@@ -20249,6 +20486,15 @@
       <c r="F18" t="inlineStr"/>
       <c r="G18" t="inlineStr"/>
       <c r="H18" t="inlineStr"/>
+      <c r="I18" t="inlineStr"/>
+      <c r="J18" t="inlineStr"/>
+      <c r="K18" t="inlineStr"/>
+      <c r="L18" t="inlineStr"/>
+      <c r="M18" t="inlineStr"/>
+      <c r="N18" t="inlineStr"/>
+      <c r="O18" t="inlineStr"/>
+      <c r="P18" t="inlineStr"/>
+      <c r="Q18" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/Aerodyne_ip_tests_summary.xlsx
+++ b/Aerodyne_ip_tests_summary.xlsx
@@ -9323,7 +9323,7 @@
       <c r="V3" t="inlineStr"/>
       <c r="W3" t="inlineStr"/>
       <c r="X3" t="n">
-        <v>46</v>
+        <v>85</v>
       </c>
       <c r="Y3" t="inlineStr"/>
       <c r="Z3" t="inlineStr"/>
@@ -9472,49 +9472,49 @@
       <c r="E6" t="inlineStr"/>
       <c r="F6" t="inlineStr">
         <is>
-          <t>VIS_0V5_Curr2_Meas</t>
+          <t>VIS_1uA_Curr1_Meas</t>
         </is>
       </c>
       <c r="G6" t="inlineStr"/>
       <c r="H6" t="inlineStr"/>
       <c r="I6" t="inlineStr">
         <is>
-          <t>VIS_1uA_Curr1_Meas</t>
+          <t>VIS_1V6_Ref_Meas</t>
         </is>
       </c>
       <c r="J6" t="inlineStr"/>
       <c r="K6" t="inlineStr"/>
       <c r="L6" t="inlineStr">
         <is>
-          <t>VIS_1V6_Ref_Meas</t>
+          <t>V-sense THD</t>
         </is>
       </c>
       <c r="M6" t="inlineStr"/>
       <c r="N6" t="inlineStr"/>
       <c r="O6" t="inlineStr">
         <is>
-          <t>V-sense THD</t>
+          <t>V-sense DNR</t>
         </is>
       </c>
       <c r="P6" t="inlineStr"/>
       <c r="Q6" t="inlineStr"/>
       <c r="R6" t="inlineStr">
         <is>
-          <t>V-sense DNR</t>
+          <t>I-sense THD</t>
         </is>
       </c>
       <c r="S6" t="inlineStr"/>
       <c r="T6" t="inlineStr"/>
       <c r="U6" t="inlineStr">
         <is>
-          <t>I-sense THD</t>
+          <t>I-sense DNR</t>
         </is>
       </c>
       <c r="V6" t="inlineStr"/>
       <c r="W6" t="inlineStr"/>
       <c r="X6" t="inlineStr">
         <is>
-          <t>I-sense DNR</t>
+          <t>VIS_0u5A_Curr2_Meas</t>
         </is>
       </c>
       <c r="Y6" t="inlineStr"/>
@@ -9550,7 +9550,7 @@
       <c r="K7" t="inlineStr"/>
       <c r="L7" t="inlineStr">
         <is>
-          <t>Tested</t>
+          <t>Compiled</t>
         </is>
       </c>
       <c r="M7" t="inlineStr"/>
@@ -9576,11 +9576,7 @@
       </c>
       <c r="V7" t="inlineStr"/>
       <c r="W7" t="inlineStr"/>
-      <c r="X7" t="inlineStr">
-        <is>
-          <t>Compiled</t>
-        </is>
-      </c>
+      <c r="X7" t="inlineStr"/>
       <c r="Y7" t="inlineStr"/>
       <c r="Z7" t="inlineStr"/>
     </row>
@@ -9640,11 +9636,7 @@
       </c>
       <c r="V8" t="inlineStr"/>
       <c r="W8" t="inlineStr"/>
-      <c r="X8" t="inlineStr">
-        <is>
-          <t>IODATA1</t>
-        </is>
-      </c>
+      <c r="X8" t="inlineStr"/>
       <c r="Y8" t="inlineStr"/>
       <c r="Z8" t="inlineStr"/>
     </row>
@@ -9678,7 +9670,7 @@
       <c r="K9" t="inlineStr"/>
       <c r="L9" t="inlineStr">
         <is>
-          <t>DC</t>
+          <t xml:space="preserve">NRZ </t>
         </is>
       </c>
       <c r="M9" t="inlineStr"/>
@@ -9704,11 +9696,7 @@
       </c>
       <c r="V9" t="inlineStr"/>
       <c r="W9" t="inlineStr"/>
-      <c r="X9" t="inlineStr">
-        <is>
-          <t xml:space="preserve">NRZ </t>
-        </is>
-      </c>
+      <c r="X9" t="inlineStr"/>
       <c r="Y9" t="inlineStr"/>
       <c r="Z9" t="inlineStr"/>
     </row>
@@ -9728,35 +9716,35 @@
       <c r="E10" t="inlineStr"/>
       <c r="F10" t="inlineStr">
         <is>
-          <t>0.45</t>
+          <t>0.9</t>
         </is>
       </c>
       <c r="G10" t="inlineStr"/>
       <c r="H10" t="inlineStr"/>
       <c r="I10" t="inlineStr">
         <is>
-          <t>0.9</t>
+          <t>1.595</t>
         </is>
       </c>
       <c r="J10" t="inlineStr"/>
       <c r="K10" t="inlineStr"/>
       <c r="L10" t="inlineStr">
         <is>
-          <t>1.595</t>
+          <t>80</t>
         </is>
       </c>
       <c r="M10" t="inlineStr"/>
       <c r="N10" t="inlineStr"/>
       <c r="O10" t="inlineStr">
         <is>
-          <t>80</t>
+          <t>90</t>
         </is>
       </c>
       <c r="P10" t="inlineStr"/>
       <c r="Q10" t="inlineStr"/>
       <c r="R10" t="inlineStr">
         <is>
-          <t>90</t>
+          <t>62</t>
         </is>
       </c>
       <c r="S10" t="inlineStr"/>
@@ -9770,7 +9758,7 @@
       <c r="W10" t="inlineStr"/>
       <c r="X10" t="inlineStr">
         <is>
-          <t>62</t>
+          <t>0.45</t>
         </is>
       </c>
       <c r="Y10" t="inlineStr"/>
@@ -9792,35 +9780,35 @@
       <c r="E11" t="inlineStr"/>
       <c r="F11" t="inlineStr">
         <is>
-          <t>0.5</t>
+          <t>1</t>
         </is>
       </c>
       <c r="G11" t="inlineStr"/>
       <c r="H11" t="inlineStr"/>
       <c r="I11" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>1.6</t>
         </is>
       </c>
       <c r="J11" t="inlineStr"/>
       <c r="K11" t="inlineStr"/>
       <c r="L11" t="inlineStr">
         <is>
-          <t>1.6</t>
+          <t>83</t>
         </is>
       </c>
       <c r="M11" t="inlineStr"/>
       <c r="N11" t="inlineStr"/>
       <c r="O11" t="inlineStr">
         <is>
-          <t>83</t>
+          <t>93</t>
         </is>
       </c>
       <c r="P11" t="inlineStr"/>
       <c r="Q11" t="inlineStr"/>
       <c r="R11" t="inlineStr">
         <is>
-          <t>93</t>
+          <t>65</t>
         </is>
       </c>
       <c r="S11" t="inlineStr"/>
@@ -9834,7 +9822,7 @@
       <c r="W11" t="inlineStr"/>
       <c r="X11" t="inlineStr">
         <is>
-          <t>65</t>
+          <t>0.5</t>
         </is>
       </c>
       <c r="Y11" t="inlineStr"/>
@@ -9856,23 +9844,19 @@
       <c r="E12" t="inlineStr"/>
       <c r="F12" t="inlineStr">
         <is>
-          <t>0.55</t>
+          <t>1.1</t>
         </is>
       </c>
       <c r="G12" t="inlineStr"/>
       <c r="H12" t="inlineStr"/>
       <c r="I12" t="inlineStr">
         <is>
-          <t>1.1</t>
+          <t>1.605</t>
         </is>
       </c>
       <c r="J12" t="inlineStr"/>
       <c r="K12" t="inlineStr"/>
-      <c r="L12" t="inlineStr">
-        <is>
-          <t>1.605</t>
-        </is>
-      </c>
+      <c r="L12" t="inlineStr"/>
       <c r="M12" t="inlineStr"/>
       <c r="N12" t="inlineStr"/>
       <c r="O12" t="inlineStr"/>
@@ -9884,7 +9868,11 @@
       <c r="U12" t="inlineStr"/>
       <c r="V12" t="inlineStr"/>
       <c r="W12" t="inlineStr"/>
-      <c r="X12" t="inlineStr"/>
+      <c r="X12" t="inlineStr">
+        <is>
+          <t>0.55</t>
+        </is>
+      </c>
       <c r="Y12" t="inlineStr"/>
       <c r="Z12" t="inlineStr"/>
     </row>
@@ -9911,14 +9899,14 @@
       <c r="H13" t="inlineStr"/>
       <c r="I13" t="inlineStr">
         <is>
-          <t>uA</t>
+          <t>V</t>
         </is>
       </c>
       <c r="J13" t="inlineStr"/>
       <c r="K13" t="inlineStr"/>
       <c r="L13" t="inlineStr">
         <is>
-          <t>V</t>
+          <t>dB</t>
         </is>
       </c>
       <c r="M13" t="inlineStr"/>
@@ -9946,7 +9934,7 @@
       <c r="W13" t="inlineStr"/>
       <c r="X13" t="inlineStr">
         <is>
-          <t>dB</t>
+          <t>uA</t>
         </is>
       </c>
       <c r="Y13" t="inlineStr"/>
@@ -9975,14 +9963,14 @@
       <c r="H14" t="inlineStr"/>
       <c r="I14" t="inlineStr">
         <is>
-          <t>10nA precision required</t>
+          <t>1mV precision required</t>
         </is>
       </c>
       <c r="J14" t="inlineStr"/>
       <c r="K14" t="inlineStr"/>
       <c r="L14" t="inlineStr">
         <is>
-          <t>1mV precision required</t>
+          <t>TDM read</t>
         </is>
       </c>
       <c r="M14" t="inlineStr"/>
@@ -10008,11 +9996,7 @@
       </c>
       <c r="V14" t="inlineStr"/>
       <c r="W14" t="inlineStr"/>
-      <c r="X14" t="inlineStr">
-        <is>
-          <t>TDM read</t>
-        </is>
-      </c>
+      <c r="X14" t="inlineStr"/>
       <c r="Y14" t="inlineStr"/>
       <c r="Z14" t="inlineStr"/>
     </row>
@@ -10277,34 +10261,34 @@
         </is>
       </c>
       <c r="E21" t="inlineStr"/>
-      <c r="F21" t="inlineStr">
-        <is>
-          <t>Measure current</t>
-        </is>
-      </c>
+      <c r="F21" t="inlineStr"/>
       <c r="G21" t="inlineStr">
         <is>
           <t>uA</t>
         </is>
       </c>
       <c r="H21" t="inlineStr"/>
-      <c r="I21" t="inlineStr"/>
-      <c r="J21" t="inlineStr">
-        <is>
-          <t>uA</t>
-        </is>
-      </c>
+      <c r="I21" t="inlineStr">
+        <is>
+          <t>Measure voltage</t>
+        </is>
+      </c>
+      <c r="J21" t="inlineStr"/>
       <c r="K21" t="inlineStr"/>
       <c r="L21" t="inlineStr">
         <is>
-          <t>Measure voltage</t>
+          <t>Acquire TDM data</t>
         </is>
       </c>
       <c r="M21" t="inlineStr"/>
-      <c r="N21" t="inlineStr"/>
+      <c r="N21" t="inlineStr">
+        <is>
+          <t>TDM SDO</t>
+        </is>
+      </c>
       <c r="O21" t="inlineStr">
         <is>
-          <t>Acquire TDM data</t>
+          <t xml:space="preserve"> Acquire TDM data</t>
         </is>
       </c>
       <c r="P21" t="inlineStr"/>
@@ -10315,7 +10299,7 @@
       </c>
       <c r="R21" t="inlineStr">
         <is>
-          <t xml:space="preserve"> Acquire TDM data</t>
+          <t>Acquire TDM data</t>
         </is>
       </c>
       <c r="S21" t="inlineStr"/>
@@ -10337,15 +10321,15 @@
       </c>
       <c r="X21" t="inlineStr">
         <is>
-          <t>Acquire TDM data</t>
-        </is>
-      </c>
-      <c r="Y21" t="inlineStr"/>
-      <c r="Z21" t="inlineStr">
-        <is>
-          <t>TDM SDO</t>
-        </is>
-      </c>
+          <t>Measure current</t>
+        </is>
+      </c>
+      <c r="Y21" t="inlineStr">
+        <is>
+          <t>uA</t>
+        </is>
+      </c>
+      <c r="Z21" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" t="n">
@@ -10597,7 +10581,11 @@
           <t>MHz</t>
         </is>
       </c>
-      <c r="N25" t="inlineStr"/>
+      <c r="N25" t="inlineStr">
+        <is>
+          <t>TDM BCLK</t>
+        </is>
+      </c>
       <c r="O25" t="inlineStr">
         <is>
           <t>3.072</t>
@@ -10653,11 +10641,7 @@
           <t>MHz</t>
         </is>
       </c>
-      <c r="Z25" t="inlineStr">
-        <is>
-          <t>TDM BCLK</t>
-        </is>
-      </c>
+      <c r="Z25" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="A26" t="n">
@@ -10843,19 +10827,19 @@
         </is>
       </c>
       <c r="E28" t="inlineStr"/>
-      <c r="F28" t="inlineStr"/>
-      <c r="G28" t="inlineStr"/>
+      <c r="F28" t="inlineStr">
+        <is>
+          <t>Measure current</t>
+        </is>
+      </c>
+      <c r="G28" t="inlineStr">
+        <is>
+          <t>uA</t>
+        </is>
+      </c>
       <c r="H28" t="inlineStr"/>
-      <c r="I28" t="inlineStr">
-        <is>
-          <t>Measure current</t>
-        </is>
-      </c>
-      <c r="J28" t="inlineStr">
-        <is>
-          <t>uA</t>
-        </is>
-      </c>
+      <c r="I28" t="inlineStr"/>
+      <c r="J28" t="inlineStr"/>
       <c r="K28" t="inlineStr"/>
       <c r="L28" t="inlineStr"/>
       <c r="M28" t="inlineStr"/>
@@ -11157,7 +11141,11 @@
       <c r="K33" t="inlineStr"/>
       <c r="L33" t="inlineStr"/>
       <c r="M33" t="inlineStr"/>
-      <c r="N33" t="inlineStr"/>
+      <c r="N33" t="inlineStr">
+        <is>
+          <t>TDM FSYN</t>
+        </is>
+      </c>
       <c r="O33" t="inlineStr"/>
       <c r="P33" t="inlineStr"/>
       <c r="Q33" t="inlineStr">
@@ -11181,11 +11169,7 @@
       </c>
       <c r="X33" t="inlineStr"/>
       <c r="Y33" t="inlineStr"/>
-      <c r="Z33" t="inlineStr">
-        <is>
-          <t>TDM FSYN</t>
-        </is>
-      </c>
+      <c r="Z33" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -11595,137 +11579,137 @@
       </c>
       <c r="B3" t="inlineStr"/>
       <c r="C3" t="n">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="D3" t="inlineStr"/>
       <c r="E3" t="inlineStr"/>
       <c r="F3" t="n">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="G3" t="inlineStr"/>
       <c r="H3" t="inlineStr"/>
       <c r="I3" t="n">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="J3" t="inlineStr"/>
       <c r="K3" t="inlineStr"/>
       <c r="L3" t="n">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="M3" t="inlineStr"/>
       <c r="N3" t="inlineStr"/>
       <c r="O3" t="n">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="P3" t="inlineStr"/>
       <c r="Q3" t="inlineStr"/>
       <c r="R3" t="n">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="S3" t="inlineStr"/>
       <c r="T3" t="inlineStr"/>
       <c r="U3" t="n">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="V3" t="inlineStr"/>
       <c r="W3" t="inlineStr"/>
       <c r="X3" t="n">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="Y3" t="inlineStr"/>
       <c r="Z3" t="inlineStr"/>
       <c r="AA3" t="n">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="AB3" t="inlineStr"/>
       <c r="AC3" t="inlineStr"/>
       <c r="AD3" t="n">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="AE3" t="inlineStr"/>
       <c r="AF3" t="inlineStr"/>
       <c r="AG3" t="n">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="AH3" t="inlineStr"/>
       <c r="AI3" t="inlineStr"/>
       <c r="AJ3" t="n">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="AK3" t="inlineStr"/>
       <c r="AL3" t="inlineStr"/>
       <c r="AM3" t="n">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="AN3" t="inlineStr"/>
       <c r="AO3" t="inlineStr"/>
       <c r="AP3" t="n">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="AQ3" t="inlineStr"/>
       <c r="AR3" t="inlineStr"/>
       <c r="AS3" t="n">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="AT3" t="inlineStr"/>
       <c r="AU3" t="inlineStr"/>
       <c r="AV3" t="n">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="AW3" t="inlineStr"/>
       <c r="AX3" t="inlineStr"/>
       <c r="AY3" t="n">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="AZ3" t="inlineStr"/>
       <c r="BA3" t="inlineStr"/>
       <c r="BB3" t="n">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="BC3" t="inlineStr"/>
       <c r="BD3" t="inlineStr"/>
       <c r="BE3" t="n">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="BF3" t="inlineStr"/>
       <c r="BG3" t="inlineStr"/>
       <c r="BH3" t="n">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="BI3" t="inlineStr"/>
       <c r="BJ3" t="inlineStr"/>
       <c r="BK3" t="n">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="BL3" t="inlineStr"/>
       <c r="BM3" t="inlineStr"/>
       <c r="BN3" t="n">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="BO3" t="inlineStr"/>
       <c r="BP3" t="inlineStr"/>
       <c r="BQ3" t="n">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="BR3" t="inlineStr"/>
       <c r="BS3" t="inlineStr"/>
       <c r="BT3" t="n">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="BU3" t="inlineStr"/>
       <c r="BV3" t="inlineStr"/>
       <c r="BW3" t="n">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="BX3" t="inlineStr"/>
       <c r="BY3" t="inlineStr"/>
       <c r="BZ3" t="n">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="CA3" t="inlineStr"/>
       <c r="CB3" t="inlineStr"/>
       <c r="CC3" t="n">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="CD3" t="inlineStr"/>
       <c r="CE3" t="inlineStr"/>
@@ -17483,22 +17467,22 @@
       </c>
       <c r="B3" t="inlineStr"/>
       <c r="C3" t="n">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="D3" t="inlineStr"/>
       <c r="E3" t="inlineStr"/>
       <c r="F3" t="n">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="G3" t="inlineStr"/>
       <c r="H3" t="inlineStr"/>
       <c r="I3" t="n">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="J3" t="inlineStr"/>
       <c r="K3" t="inlineStr"/>
       <c r="L3" t="n">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="M3" t="inlineStr"/>
       <c r="N3" t="inlineStr"/>
@@ -18644,42 +18628,42 @@
       </c>
       <c r="B3" t="inlineStr"/>
       <c r="C3" t="n">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="D3" t="inlineStr"/>
       <c r="E3" t="inlineStr"/>
       <c r="F3" t="n">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="G3" t="inlineStr"/>
       <c r="H3" t="inlineStr"/>
       <c r="I3" t="n">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="J3" t="inlineStr"/>
       <c r="K3" t="inlineStr"/>
       <c r="L3" t="n">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="M3" t="inlineStr"/>
       <c r="N3" t="inlineStr"/>
       <c r="O3" t="n">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="P3" t="inlineStr"/>
       <c r="Q3" t="inlineStr"/>
       <c r="R3" t="n">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="S3" t="inlineStr"/>
       <c r="T3" t="inlineStr"/>
       <c r="U3" t="n">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="V3" t="inlineStr"/>
       <c r="W3" t="inlineStr"/>
       <c r="X3" t="n">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="Y3" t="inlineStr"/>
       <c r="Z3" t="inlineStr"/>

--- a/Aerodyne_ip_tests_summary.xlsx
+++ b/Aerodyne_ip_tests_summary.xlsx
@@ -9323,7 +9323,7 @@
       <c r="V3" t="inlineStr"/>
       <c r="W3" t="inlineStr"/>
       <c r="X3" t="n">
-        <v>85</v>
+        <v>46</v>
       </c>
       <c r="Y3" t="inlineStr"/>
       <c r="Z3" t="inlineStr"/>
@@ -9465,49 +9465,49 @@
       <c r="B6" t="inlineStr"/>
       <c r="C6" t="inlineStr">
         <is>
-          <t>VIS_1V5_Meas</t>
+          <t>VIS_1uA_Curr1_Meas</t>
         </is>
       </c>
       <c r="D6" t="inlineStr"/>
       <c r="E6" t="inlineStr"/>
       <c r="F6" t="inlineStr">
         <is>
-          <t>VIS_1uA_Curr1_Meas</t>
+          <t>VIS_1V6_Ref_Meas</t>
         </is>
       </c>
       <c r="G6" t="inlineStr"/>
       <c r="H6" t="inlineStr"/>
       <c r="I6" t="inlineStr">
         <is>
-          <t>VIS_1V6_Ref_Meas</t>
+          <t>V-sense THD</t>
         </is>
       </c>
       <c r="J6" t="inlineStr"/>
       <c r="K6" t="inlineStr"/>
       <c r="L6" t="inlineStr">
         <is>
-          <t>V-sense THD</t>
+          <t>V-sense DNR</t>
         </is>
       </c>
       <c r="M6" t="inlineStr"/>
       <c r="N6" t="inlineStr"/>
       <c r="O6" t="inlineStr">
         <is>
-          <t>V-sense DNR</t>
+          <t>I-sense THD</t>
         </is>
       </c>
       <c r="P6" t="inlineStr"/>
       <c r="Q6" t="inlineStr"/>
       <c r="R6" t="inlineStr">
         <is>
-          <t>I-sense THD</t>
+          <t>I-sense DNR</t>
         </is>
       </c>
       <c r="S6" t="inlineStr"/>
       <c r="T6" t="inlineStr"/>
       <c r="U6" t="inlineStr">
         <is>
-          <t>I-sense DNR</t>
+          <t>VIS_1V5_Meas</t>
         </is>
       </c>
       <c r="V6" t="inlineStr"/>
@@ -9543,7 +9543,7 @@
       <c r="H7" t="inlineStr"/>
       <c r="I7" t="inlineStr">
         <is>
-          <t>Tested</t>
+          <t>Compiled</t>
         </is>
       </c>
       <c r="J7" t="inlineStr"/>
@@ -9571,12 +9571,16 @@
       <c r="T7" t="inlineStr"/>
       <c r="U7" t="inlineStr">
         <is>
-          <t>Compiled</t>
+          <t>Tested</t>
         </is>
       </c>
       <c r="V7" t="inlineStr"/>
       <c r="W7" t="inlineStr"/>
-      <c r="X7" t="inlineStr"/>
+      <c r="X7" t="inlineStr">
+        <is>
+          <t>Tested</t>
+        </is>
+      </c>
       <c r="Y7" t="inlineStr"/>
       <c r="Z7" t="inlineStr"/>
     </row>
@@ -9631,7 +9635,7 @@
       <c r="T8" t="inlineStr"/>
       <c r="U8" t="inlineStr">
         <is>
-          <t>IODATA1</t>
+          <t>IODATA1/ADDR</t>
         </is>
       </c>
       <c r="V8" t="inlineStr"/>
@@ -9663,7 +9667,7 @@
       <c r="H9" t="inlineStr"/>
       <c r="I9" t="inlineStr">
         <is>
-          <t>DC</t>
+          <t xml:space="preserve">NRZ </t>
         </is>
       </c>
       <c r="J9" t="inlineStr"/>
@@ -9691,7 +9695,7 @@
       <c r="T9" t="inlineStr"/>
       <c r="U9" t="inlineStr">
         <is>
-          <t xml:space="preserve">NRZ </t>
+          <t>DC</t>
         </is>
       </c>
       <c r="V9" t="inlineStr"/>
@@ -9709,35 +9713,35 @@
       <c r="B10" t="inlineStr"/>
       <c r="C10" t="inlineStr">
         <is>
-          <t>1.495</t>
+          <t>0.9</t>
         </is>
       </c>
       <c r="D10" t="inlineStr"/>
       <c r="E10" t="inlineStr"/>
       <c r="F10" t="inlineStr">
         <is>
-          <t>0.9</t>
+          <t>1.595</t>
         </is>
       </c>
       <c r="G10" t="inlineStr"/>
       <c r="H10" t="inlineStr"/>
       <c r="I10" t="inlineStr">
         <is>
-          <t>1.595</t>
+          <t>80</t>
         </is>
       </c>
       <c r="J10" t="inlineStr"/>
       <c r="K10" t="inlineStr"/>
       <c r="L10" t="inlineStr">
         <is>
-          <t>80</t>
+          <t>90</t>
         </is>
       </c>
       <c r="M10" t="inlineStr"/>
       <c r="N10" t="inlineStr"/>
       <c r="O10" t="inlineStr">
         <is>
-          <t>90</t>
+          <t>62</t>
         </is>
       </c>
       <c r="P10" t="inlineStr"/>
@@ -9751,7 +9755,7 @@
       <c r="T10" t="inlineStr"/>
       <c r="U10" t="inlineStr">
         <is>
-          <t>62</t>
+          <t>1.495</t>
         </is>
       </c>
       <c r="V10" t="inlineStr"/>
@@ -9773,35 +9777,35 @@
       <c r="B11" t="inlineStr"/>
       <c r="C11" t="inlineStr">
         <is>
-          <t>1.5</t>
+          <t>1</t>
         </is>
       </c>
       <c r="D11" t="inlineStr"/>
       <c r="E11" t="inlineStr"/>
       <c r="F11" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>1.6</t>
         </is>
       </c>
       <c r="G11" t="inlineStr"/>
       <c r="H11" t="inlineStr"/>
       <c r="I11" t="inlineStr">
         <is>
-          <t>1.6</t>
+          <t>83</t>
         </is>
       </c>
       <c r="J11" t="inlineStr"/>
       <c r="K11" t="inlineStr"/>
       <c r="L11" t="inlineStr">
         <is>
-          <t>83</t>
+          <t>93</t>
         </is>
       </c>
       <c r="M11" t="inlineStr"/>
       <c r="N11" t="inlineStr"/>
       <c r="O11" t="inlineStr">
         <is>
-          <t>93</t>
+          <t>65</t>
         </is>
       </c>
       <c r="P11" t="inlineStr"/>
@@ -9815,7 +9819,7 @@
       <c r="T11" t="inlineStr"/>
       <c r="U11" t="inlineStr">
         <is>
-          <t>65</t>
+          <t>1.5</t>
         </is>
       </c>
       <c r="V11" t="inlineStr"/>
@@ -9837,23 +9841,19 @@
       <c r="B12" t="inlineStr"/>
       <c r="C12" t="inlineStr">
         <is>
-          <t>1.505</t>
+          <t>1.1</t>
         </is>
       </c>
       <c r="D12" t="inlineStr"/>
       <c r="E12" t="inlineStr"/>
       <c r="F12" t="inlineStr">
         <is>
-          <t>1.1</t>
+          <t>1.605</t>
         </is>
       </c>
       <c r="G12" t="inlineStr"/>
       <c r="H12" t="inlineStr"/>
-      <c r="I12" t="inlineStr">
-        <is>
-          <t>1.605</t>
-        </is>
-      </c>
+      <c r="I12" t="inlineStr"/>
       <c r="J12" t="inlineStr"/>
       <c r="K12" t="inlineStr"/>
       <c r="L12" t="inlineStr"/>
@@ -9865,7 +9865,11 @@
       <c r="R12" t="inlineStr"/>
       <c r="S12" t="inlineStr"/>
       <c r="T12" t="inlineStr"/>
-      <c r="U12" t="inlineStr"/>
+      <c r="U12" t="inlineStr">
+        <is>
+          <t>1.505</t>
+        </is>
+      </c>
       <c r="V12" t="inlineStr"/>
       <c r="W12" t="inlineStr"/>
       <c r="X12" t="inlineStr">
@@ -9885,21 +9889,21 @@
       <c r="B13" t="inlineStr"/>
       <c r="C13" t="inlineStr">
         <is>
-          <t>V</t>
+          <t>uA</t>
         </is>
       </c>
       <c r="D13" t="inlineStr"/>
       <c r="E13" t="inlineStr"/>
       <c r="F13" t="inlineStr">
         <is>
-          <t>uA</t>
+          <t>V</t>
         </is>
       </c>
       <c r="G13" t="inlineStr"/>
       <c r="H13" t="inlineStr"/>
       <c r="I13" t="inlineStr">
         <is>
-          <t>V</t>
+          <t>dB</t>
         </is>
       </c>
       <c r="J13" t="inlineStr"/>
@@ -9927,7 +9931,7 @@
       <c r="T13" t="inlineStr"/>
       <c r="U13" t="inlineStr">
         <is>
-          <t>dB</t>
+          <t>V</t>
         </is>
       </c>
       <c r="V13" t="inlineStr"/>
@@ -9949,21 +9953,21 @@
       <c r="B14" t="inlineStr"/>
       <c r="C14" t="inlineStr">
         <is>
-          <t>1mV precision required</t>
+          <t>10nA precision required</t>
         </is>
       </c>
       <c r="D14" t="inlineStr"/>
       <c r="E14" t="inlineStr"/>
       <c r="F14" t="inlineStr">
         <is>
-          <t>10nA precision required</t>
+          <t>1mV precision required</t>
         </is>
       </c>
       <c r="G14" t="inlineStr"/>
       <c r="H14" t="inlineStr"/>
       <c r="I14" t="inlineStr">
         <is>
-          <t>1mV precision required</t>
+          <t>TDM read</t>
         </is>
       </c>
       <c r="J14" t="inlineStr"/>
@@ -9989,11 +9993,7 @@
       </c>
       <c r="S14" t="inlineStr"/>
       <c r="T14" t="inlineStr"/>
-      <c r="U14" t="inlineStr">
-        <is>
-          <t>TDM read</t>
-        </is>
-      </c>
+      <c r="U14" t="inlineStr"/>
       <c r="V14" t="inlineStr"/>
       <c r="W14" t="inlineStr"/>
       <c r="X14" t="inlineStr"/>
@@ -10250,34 +10250,34 @@
           <t>IODATA1</t>
         </is>
       </c>
-      <c r="C21" t="inlineStr">
+      <c r="C21" t="inlineStr"/>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>uA</t>
+        </is>
+      </c>
+      <c r="E21" t="inlineStr"/>
+      <c r="F21" t="inlineStr">
         <is>
           <t>Measure voltage</t>
         </is>
       </c>
-      <c r="D21" t="inlineStr">
-        <is>
-          <t>V</t>
-        </is>
-      </c>
-      <c r="E21" t="inlineStr"/>
-      <c r="F21" t="inlineStr"/>
-      <c r="G21" t="inlineStr">
-        <is>
-          <t>uA</t>
-        </is>
-      </c>
+      <c r="G21" t="inlineStr"/>
       <c r="H21" t="inlineStr"/>
       <c r="I21" t="inlineStr">
         <is>
-          <t>Measure voltage</t>
+          <t>Acquire TDM data</t>
         </is>
       </c>
       <c r="J21" t="inlineStr"/>
-      <c r="K21" t="inlineStr"/>
+      <c r="K21" t="inlineStr">
+        <is>
+          <t>TDM SDO</t>
+        </is>
+      </c>
       <c r="L21" t="inlineStr">
         <is>
-          <t>Acquire TDM data</t>
+          <t xml:space="preserve"> Acquire TDM data</t>
         </is>
       </c>
       <c r="M21" t="inlineStr"/>
@@ -10288,7 +10288,7 @@
       </c>
       <c r="O21" t="inlineStr">
         <is>
-          <t xml:space="preserve"> Acquire TDM data</t>
+          <t>Acquire TDM data</t>
         </is>
       </c>
       <c r="P21" t="inlineStr"/>
@@ -10310,15 +10310,15 @@
       </c>
       <c r="U21" t="inlineStr">
         <is>
-          <t>Acquire TDM data</t>
-        </is>
-      </c>
-      <c r="V21" t="inlineStr"/>
-      <c r="W21" t="inlineStr">
-        <is>
-          <t>TDM SDO</t>
-        </is>
-      </c>
+          <t>Measure voltage</t>
+        </is>
+      </c>
+      <c r="V21" t="inlineStr">
+        <is>
+          <t>V</t>
+        </is>
+      </c>
+      <c r="W21" t="inlineStr"/>
       <c r="X21" t="inlineStr">
         <is>
           <t>Measure current</t>
@@ -10570,7 +10570,11 @@
           <t>MHz</t>
         </is>
       </c>
-      <c r="K25" t="inlineStr"/>
+      <c r="K25" t="inlineStr">
+        <is>
+          <t>TDM BCLK</t>
+        </is>
+      </c>
       <c r="L25" t="inlineStr">
         <is>
           <t>3.072</t>
@@ -10626,11 +10630,7 @@
           <t>MHz</t>
         </is>
       </c>
-      <c r="W25" t="inlineStr">
-        <is>
-          <t>TDM BCLK</t>
-        </is>
-      </c>
+      <c r="W25" t="inlineStr"/>
       <c r="X25" t="inlineStr">
         <is>
           <t>3.072</t>
@@ -10818,25 +10818,17 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Measure voltage</t>
+          <t>Measure current</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>V</t>
+          <t>uA</t>
         </is>
       </c>
       <c r="E28" t="inlineStr"/>
-      <c r="F28" t="inlineStr">
-        <is>
-          <t>Measure current</t>
-        </is>
-      </c>
-      <c r="G28" t="inlineStr">
-        <is>
-          <t>uA</t>
-        </is>
-      </c>
+      <c r="F28" t="inlineStr"/>
+      <c r="G28" t="inlineStr"/>
       <c r="H28" t="inlineStr"/>
       <c r="I28" t="inlineStr"/>
       <c r="J28" t="inlineStr"/>
@@ -10850,8 +10842,16 @@
       <c r="R28" t="inlineStr"/>
       <c r="S28" t="inlineStr"/>
       <c r="T28" t="inlineStr"/>
-      <c r="U28" t="inlineStr"/>
-      <c r="V28" t="inlineStr"/>
+      <c r="U28" t="inlineStr">
+        <is>
+          <t>Measure voltage</t>
+        </is>
+      </c>
+      <c r="V28" t="inlineStr">
+        <is>
+          <t>V</t>
+        </is>
+      </c>
       <c r="W28" t="inlineStr"/>
       <c r="X28" t="inlineStr"/>
       <c r="Y28" t="inlineStr"/>
@@ -11138,7 +11138,11 @@
       <c r="H33" t="inlineStr"/>
       <c r="I33" t="inlineStr"/>
       <c r="J33" t="inlineStr"/>
-      <c r="K33" t="inlineStr"/>
+      <c r="K33" t="inlineStr">
+        <is>
+          <t>TDM FSYN</t>
+        </is>
+      </c>
       <c r="L33" t="inlineStr"/>
       <c r="M33" t="inlineStr"/>
       <c r="N33" t="inlineStr">
@@ -11162,11 +11166,7 @@
       </c>
       <c r="U33" t="inlineStr"/>
       <c r="V33" t="inlineStr"/>
-      <c r="W33" t="inlineStr">
-        <is>
-          <t>TDM FSYN</t>
-        </is>
-      </c>
+      <c r="W33" t="inlineStr"/>
       <c r="X33" t="inlineStr"/>
       <c r="Y33" t="inlineStr"/>
       <c r="Z33" t="inlineStr"/>
@@ -11579,137 +11579,137 @@
       </c>
       <c r="B3" t="inlineStr"/>
       <c r="C3" t="n">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="D3" t="inlineStr"/>
       <c r="E3" t="inlineStr"/>
       <c r="F3" t="n">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="G3" t="inlineStr"/>
       <c r="H3" t="inlineStr"/>
       <c r="I3" t="n">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="J3" t="inlineStr"/>
       <c r="K3" t="inlineStr"/>
       <c r="L3" t="n">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="M3" t="inlineStr"/>
       <c r="N3" t="inlineStr"/>
       <c r="O3" t="n">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="P3" t="inlineStr"/>
       <c r="Q3" t="inlineStr"/>
       <c r="R3" t="n">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="S3" t="inlineStr"/>
       <c r="T3" t="inlineStr"/>
       <c r="U3" t="n">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="V3" t="inlineStr"/>
       <c r="W3" t="inlineStr"/>
       <c r="X3" t="n">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="Y3" t="inlineStr"/>
       <c r="Z3" t="inlineStr"/>
       <c r="AA3" t="n">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="AB3" t="inlineStr"/>
       <c r="AC3" t="inlineStr"/>
       <c r="AD3" t="n">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="AE3" t="inlineStr"/>
       <c r="AF3" t="inlineStr"/>
       <c r="AG3" t="n">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="AH3" t="inlineStr"/>
       <c r="AI3" t="inlineStr"/>
       <c r="AJ3" t="n">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="AK3" t="inlineStr"/>
       <c r="AL3" t="inlineStr"/>
       <c r="AM3" t="n">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="AN3" t="inlineStr"/>
       <c r="AO3" t="inlineStr"/>
       <c r="AP3" t="n">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="AQ3" t="inlineStr"/>
       <c r="AR3" t="inlineStr"/>
       <c r="AS3" t="n">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="AT3" t="inlineStr"/>
       <c r="AU3" t="inlineStr"/>
       <c r="AV3" t="n">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="AW3" t="inlineStr"/>
       <c r="AX3" t="inlineStr"/>
       <c r="AY3" t="n">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="AZ3" t="inlineStr"/>
       <c r="BA3" t="inlineStr"/>
       <c r="BB3" t="n">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="BC3" t="inlineStr"/>
       <c r="BD3" t="inlineStr"/>
       <c r="BE3" t="n">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="BF3" t="inlineStr"/>
       <c r="BG3" t="inlineStr"/>
       <c r="BH3" t="n">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="BI3" t="inlineStr"/>
       <c r="BJ3" t="inlineStr"/>
       <c r="BK3" t="n">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="BL3" t="inlineStr"/>
       <c r="BM3" t="inlineStr"/>
       <c r="BN3" t="n">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="BO3" t="inlineStr"/>
       <c r="BP3" t="inlineStr"/>
       <c r="BQ3" t="n">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="BR3" t="inlineStr"/>
       <c r="BS3" t="inlineStr"/>
       <c r="BT3" t="n">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="BU3" t="inlineStr"/>
       <c r="BV3" t="inlineStr"/>
       <c r="BW3" t="n">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="BX3" t="inlineStr"/>
       <c r="BY3" t="inlineStr"/>
       <c r="BZ3" t="n">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="CA3" t="inlineStr"/>
       <c r="CB3" t="inlineStr"/>
       <c r="CC3" t="n">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="CD3" t="inlineStr"/>
       <c r="CE3" t="inlineStr"/>
@@ -12405,7 +12405,7 @@
       <c r="AO7" t="inlineStr"/>
       <c r="AP7" t="inlineStr">
         <is>
-          <t>Compiled</t>
+          <t>Tested</t>
         </is>
       </c>
       <c r="AQ7" t="inlineStr"/>
@@ -17467,22 +17467,22 @@
       </c>
       <c r="B3" t="inlineStr"/>
       <c r="C3" t="n">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="D3" t="inlineStr"/>
       <c r="E3" t="inlineStr"/>
       <c r="F3" t="n">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="G3" t="inlineStr"/>
       <c r="H3" t="inlineStr"/>
       <c r="I3" t="n">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="J3" t="inlineStr"/>
       <c r="K3" t="inlineStr"/>
       <c r="L3" t="n">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="M3" t="inlineStr"/>
       <c r="N3" t="inlineStr"/>
@@ -17824,28 +17824,28 @@
       <c r="B14" t="inlineStr"/>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Bug / Not @ATE</t>
+          <t>Bug in GPADC Offset</t>
         </is>
       </c>
       <c r="D14" t="inlineStr"/>
       <c r="E14" t="inlineStr"/>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Bug / Not @ATE</t>
+          <t>Bug in GPADC Offset</t>
         </is>
       </c>
       <c r="G14" t="inlineStr"/>
       <c r="H14" t="inlineStr"/>
       <c r="I14" t="inlineStr">
         <is>
-          <t>Bug / Not @ATE</t>
+          <t>Bug in GPADC Offset</t>
         </is>
       </c>
       <c r="J14" t="inlineStr"/>
       <c r="K14" t="inlineStr"/>
       <c r="L14" t="inlineStr">
         <is>
-          <t>Bug / Not @ATE</t>
+          <t>Bug in GPADC Offset</t>
         </is>
       </c>
       <c r="M14" t="inlineStr"/>
@@ -18628,42 +18628,42 @@
       </c>
       <c r="B3" t="inlineStr"/>
       <c r="C3" t="n">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="D3" t="inlineStr"/>
       <c r="E3" t="inlineStr"/>
       <c r="F3" t="n">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="G3" t="inlineStr"/>
       <c r="H3" t="inlineStr"/>
       <c r="I3" t="n">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="J3" t="inlineStr"/>
       <c r="K3" t="inlineStr"/>
       <c r="L3" t="n">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="M3" t="inlineStr"/>
       <c r="N3" t="inlineStr"/>
       <c r="O3" t="n">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="P3" t="inlineStr"/>
       <c r="Q3" t="inlineStr"/>
       <c r="R3" t="n">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="S3" t="inlineStr"/>
       <c r="T3" t="inlineStr"/>
       <c r="U3" t="n">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="V3" t="inlineStr"/>
       <c r="W3" t="inlineStr"/>
       <c r="X3" t="n">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="Y3" t="inlineStr"/>
       <c r="Z3" t="inlineStr"/>
@@ -18867,19 +18867,39 @@
         </is>
       </c>
       <c r="B7" t="inlineStr"/>
-      <c r="C7" t="inlineStr"/>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>Tested</t>
+        </is>
+      </c>
       <c r="D7" t="inlineStr"/>
       <c r="E7" t="inlineStr"/>
-      <c r="F7" t="inlineStr"/>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>Tested</t>
+        </is>
+      </c>
       <c r="G7" t="inlineStr"/>
       <c r="H7" t="inlineStr"/>
-      <c r="I7" t="inlineStr"/>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>Tested</t>
+        </is>
+      </c>
       <c r="J7" t="inlineStr"/>
       <c r="K7" t="inlineStr"/>
-      <c r="L7" t="inlineStr"/>
+      <c r="L7" t="inlineStr">
+        <is>
+          <t>Tested</t>
+        </is>
+      </c>
       <c r="M7" t="inlineStr"/>
       <c r="N7" t="inlineStr"/>
-      <c r="O7" t="inlineStr"/>
+      <c r="O7" t="inlineStr">
+        <is>
+          <t>Tested</t>
+        </is>
+      </c>
       <c r="P7" t="inlineStr"/>
       <c r="Q7" t="inlineStr"/>
       <c r="R7" t="inlineStr">
@@ -18889,10 +18909,18 @@
       </c>
       <c r="S7" t="inlineStr"/>
       <c r="T7" t="inlineStr"/>
-      <c r="U7" t="inlineStr"/>
+      <c r="U7" t="inlineStr">
+        <is>
+          <t>Tested</t>
+        </is>
+      </c>
       <c r="V7" t="inlineStr"/>
       <c r="W7" t="inlineStr"/>
-      <c r="X7" t="inlineStr"/>
+      <c r="X7" t="inlineStr">
+        <is>
+          <t>Tested</t>
+        </is>
+      </c>
       <c r="Y7" t="inlineStr"/>
       <c r="Z7" t="inlineStr"/>
     </row>
@@ -20347,19 +20375,39 @@
         </is>
       </c>
       <c r="B14" t="inlineStr"/>
-      <c r="C14" t="inlineStr"/>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>Not @ATE</t>
+        </is>
+      </c>
       <c r="D14" t="inlineStr"/>
       <c r="E14" t="inlineStr"/>
-      <c r="F14" t="inlineStr"/>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>Not @ATE</t>
+        </is>
+      </c>
       <c r="G14" t="inlineStr"/>
       <c r="H14" t="inlineStr"/>
-      <c r="I14" t="inlineStr"/>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>Not @ATE</t>
+        </is>
+      </c>
       <c r="J14" t="inlineStr"/>
       <c r="K14" t="inlineStr"/>
-      <c r="L14" t="inlineStr"/>
+      <c r="L14" t="inlineStr">
+        <is>
+          <t>Not @ATE</t>
+        </is>
+      </c>
       <c r="M14" t="inlineStr"/>
       <c r="N14" t="inlineStr"/>
-      <c r="O14" t="inlineStr"/>
+      <c r="O14" t="inlineStr">
+        <is>
+          <t>Not @ATE</t>
+        </is>
+      </c>
       <c r="P14" t="inlineStr"/>
       <c r="Q14" t="inlineStr"/>
     </row>
